--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gessi\sdg-data-rwanda\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76E839F-06C6-46B8-A096-F7093E4B6C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644880C9-9EA3-4A32-8448-43B521AA4297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$AT$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$AT$514</definedName>
     <definedName name="CL_REF_AREA_DESCRIPTION">[1]VAL_REF_AREA!$A$2:$B$573</definedName>
     <definedName name="CL_REPORTING_TYPE_DESCRIPTION">[1]VAL_REPORTING_TYPE!$A$2:$B$4</definedName>
     <definedName name="CL_SERIES_DESCRIPTION">[1]VAL_SERIES!$A$2:$B$307</definedName>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6912" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7120" uniqueCount="1075">
   <si>
     <t>Indicator</t>
   </si>
@@ -3169,21 +3169,6 @@
     <t>Macroeconomic Dashboard</t>
   </si>
   <si>
-    <t>MD_NY_GDP_PCAP</t>
-  </si>
-  <si>
-    <t>MD_SL_TLF_UEM</t>
-  </si>
-  <si>
-    <t>MD_CPI</t>
-  </si>
-  <si>
-    <t>Price Statistics, NISR</t>
-  </si>
-  <si>
-    <t>Consumer Price Index (CPI), annual at February</t>
-  </si>
-  <si>
     <t>Number of deaths due to disaster per 100,000 population</t>
   </si>
   <si>
@@ -3254,6 +3239,123 @@
   </si>
   <si>
     <t>_L_RW_110502_5</t>
+  </si>
+  <si>
+    <t>BN_CAB_XOKA_GD_ZS</t>
+  </si>
+  <si>
+    <t>BN_KLT_PTXL_CD</t>
+  </si>
+  <si>
+    <t>Portfolio investment, net (Balance of Payments, million USD)</t>
+  </si>
+  <si>
+    <t>BX_KLT_DINV_WD_GD_ZS</t>
+  </si>
+  <si>
+    <t>Foreign direct investment as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>Current account balance as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>DP_DOD_DLD2_CR_CG_Z1</t>
+  </si>
+  <si>
+    <t>Gross public sector debt, Central Government, as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>DT_DOD_DECT_GN_ZS</t>
+  </si>
+  <si>
+    <t>External debt stocks as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>FB_BNK_CAPA_ZS</t>
+  </si>
+  <si>
+    <t>Bank capital adequacy ratio</t>
+  </si>
+  <si>
+    <t>FI_RES_TOTL_MO</t>
+  </si>
+  <si>
+    <t>Gross official reserves in months of next year's imports (ratio)</t>
+  </si>
+  <si>
+    <t>FM_LBL_BMNY_ZG</t>
+  </si>
+  <si>
+    <t>Annual broad money growth</t>
+  </si>
+  <si>
+    <t>FP_CPI_TOTL_ZG</t>
+  </si>
+  <si>
+    <t>Annual inflation, CPI period average percentage change</t>
+  </si>
+  <si>
+    <t>GC_BAL_CASH_GD_ZS</t>
+  </si>
+  <si>
+    <t>Fiscal deficit (including grants) as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>GC_TAX_TOTL_GD_ZS</t>
+  </si>
+  <si>
+    <t>Tax revenue as a percentage of GDP</t>
+  </si>
+  <si>
+    <t>Budget Framework Paper, MINECOFIN</t>
+  </si>
+  <si>
+    <t>NE_CON_GOVT_KD_ZG</t>
+  </si>
+  <si>
+    <t>NE_CON_PRVT_KD_ZG</t>
+  </si>
+  <si>
+    <t>NE_GDI_TOTL_KD_ZG</t>
+  </si>
+  <si>
+    <t>NE_EXP_GNFS_KD_ZG</t>
+  </si>
+  <si>
+    <t>NE_IMP_GNFS_KD_ZG</t>
+  </si>
+  <si>
+    <t>Annual growth of the general government final consumption expenditure</t>
+  </si>
+  <si>
+    <t>Annual growth of households and NGOs final consumption expenditure</t>
+  </si>
+  <si>
+    <t>Annual growth of the gross capital formation</t>
+  </si>
+  <si>
+    <t>Annual growth of exports of goods and services</t>
+  </si>
+  <si>
+    <t>Annual growth of imports of goods and services</t>
+  </si>
+  <si>
+    <t>Annual GDP growth</t>
+  </si>
+  <si>
+    <t>NY_GDP_MKTP_KD_ZG</t>
+  </si>
+  <si>
+    <t>PA_NUS_ATLS</t>
+  </si>
+  <si>
+    <t>Annual average national currency per United States dollar</t>
+  </si>
+  <si>
+    <t>TG_VAL_TOTL_GD_ZS</t>
+  </si>
+  <si>
+    <t>Total trade in goods and services as a percentage of GDP</t>
   </si>
 </sst>
 </file>
@@ -3261,9 +3363,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -3380,8 +3482,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3395,7 +3497,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="10">
@@ -11063,8 +11165,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT498"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AT514"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="10.6328125" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -11073,7 +11175,7 @@
     <col min="22" max="46" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11213,7 +11315,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -11269,7 +11371,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -11328,7 +11430,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -11384,7 +11486,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -11440,7 +11542,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -11496,7 +11598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -11552,7 +11654,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="8" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -11611,7 +11713,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="9" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11670,7 +11772,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="10" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -11732,7 +11834,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="11" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -11794,7 +11896,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -11856,7 +11958,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="13" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -11918,7 +12020,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -11980,7 +12082,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="15" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -12036,7 +12138,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="16" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -12092,7 +12194,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="17" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -12148,7 +12250,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="18" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -12204,7 +12306,7 @@
         <v>43.3</v>
       </c>
     </row>
-    <row r="19" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -12260,7 +12362,7 @@
         <v>45.6</v>
       </c>
     </row>
-    <row r="20" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -12316,7 +12418,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -12372,7 +12474,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="22" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -12428,7 +12530,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="23" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -12484,7 +12586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -12540,7 +12642,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -12596,7 +12698,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -12652,7 +12754,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -12708,7 +12810,7 @@
         <v>40.799999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -12764,7 +12866,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -12820,7 +12922,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="30" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -12876,7 +12978,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="31" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -12932,7 +13034,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="32" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -12988,7 +13090,7 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="33" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -13044,7 +13146,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="34" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -13100,7 +13202,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="35" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -13156,7 +13258,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -13212,7 +13314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -13268,7 +13370,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="38" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -13324,7 +13426,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="39" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -13380,7 +13482,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="40" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -13436,7 +13538,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -13492,7 +13594,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="42" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -13548,7 +13650,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="43" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -13604,7 +13706,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="44" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -13660,7 +13762,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="45" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A45" t="s">
         <v>123</v>
       </c>
@@ -13725,7 +13827,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A46" t="s">
         <v>123</v>
       </c>
@@ -13787,7 +13889,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A47" t="s">
         <v>123</v>
       </c>
@@ -13849,7 +13951,7 @@
         <v>0.16400000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A48" t="s">
         <v>123</v>
       </c>
@@ -13911,7 +14013,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -13973,7 +14075,7 @@
         <v>0.158</v>
       </c>
     </row>
-    <row r="50" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A50" t="s">
         <v>123</v>
       </c>
@@ -14035,7 +14137,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A51" t="s">
         <v>123</v>
       </c>
@@ -14097,7 +14199,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="52" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A52" t="s">
         <v>123</v>
       </c>
@@ -14159,7 +14261,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="53" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A53" t="s">
         <v>127</v>
       </c>
@@ -14209,7 +14311,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A54" t="s">
         <v>127</v>
       </c>
@@ -14262,7 +14364,7 @@
         <v>705713</v>
       </c>
     </row>
-    <row r="55" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A55" t="s">
         <v>127</v>
       </c>
@@ -14321,7 +14423,7 @@
         <v>608436</v>
       </c>
     </row>
-    <row r="56" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A56" t="s">
         <v>127</v>
       </c>
@@ -14374,7 +14476,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="57" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -14427,7 +14529,7 @@
         <v>97.3</v>
       </c>
     </row>
-    <row r="58" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A58" t="s">
         <v>127</v>
       </c>
@@ -14483,7 +14585,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="59" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A59" t="s">
         <v>127</v>
       </c>
@@ -14539,7 +14641,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="60" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A60" t="s">
         <v>127</v>
       </c>
@@ -14595,7 +14697,7 @@
         <v>97.1</v>
       </c>
     </row>
-    <row r="61" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A61" t="s">
         <v>127</v>
       </c>
@@ -14651,7 +14753,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="62" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A62" t="s">
         <v>127</v>
       </c>
@@ -14701,7 +14803,7 @@
         <v>233982</v>
       </c>
     </row>
-    <row r="63" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A63" t="s">
         <v>51</v>
       </c>
@@ -14745,7 +14847,7 @@
         <v>38.200000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -14792,7 +14894,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="65" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A65" t="s">
         <v>51</v>
       </c>
@@ -14839,7 +14941,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="66" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A66" t="s">
         <v>130</v>
       </c>
@@ -14883,7 +14985,7 @@
         <v>4218003</v>
       </c>
     </row>
-    <row r="67" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A67" t="s">
         <v>130</v>
       </c>
@@ -14930,7 +15032,7 @@
         <v>2081442</v>
       </c>
     </row>
-    <row r="68" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A68" t="s">
         <v>130</v>
       </c>
@@ -14977,7 +15079,7 @@
         <v>2136561</v>
       </c>
     </row>
-    <row r="69" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A69" t="s">
         <v>130</v>
       </c>
@@ -15021,7 +15123,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A70" t="s">
         <v>132</v>
       </c>
@@ -15053,7 +15155,7 @@
         <v>973</v>
       </c>
       <c r="P70" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="R70" t="s">
         <v>89</v>
@@ -15089,7 +15191,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="71" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A71" t="s">
         <v>132</v>
       </c>
@@ -15121,7 +15223,7 @@
         <v>973</v>
       </c>
       <c r="P71" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="R71" t="s">
         <v>89</v>
@@ -15157,7 +15259,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="72" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A72" t="s">
         <v>940</v>
       </c>
@@ -15219,7 +15321,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="73" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A73" t="s">
         <v>940</v>
       </c>
@@ -15281,7 +15383,7 @@
         <v>1355.3</v>
       </c>
     </row>
-    <row r="74" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A74" t="s">
         <v>940</v>
       </c>
@@ -15343,7 +15445,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="75" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A75" t="s">
         <v>940</v>
       </c>
@@ -15405,7 +15507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A76" t="s">
         <v>940</v>
       </c>
@@ -15467,7 +15569,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A77" t="s">
         <v>940</v>
       </c>
@@ -15529,7 +15631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A78" t="s">
         <v>940</v>
       </c>
@@ -15591,7 +15693,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="79" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A79" t="s">
         <v>940</v>
       </c>
@@ -15653,7 +15755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A80" t="s">
         <v>940</v>
       </c>
@@ -15712,7 +15814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>940</v>
       </c>
@@ -15771,7 +15873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>940</v>
       </c>
@@ -15827,7 +15929,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>940</v>
       </c>
@@ -15886,7 +15988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>940</v>
       </c>
@@ -15945,7 +16047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>940</v>
       </c>
@@ -16004,7 +16106,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>133</v>
       </c>
@@ -16066,7 +16168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>135</v>
       </c>
@@ -16116,7 +16218,7 @@
         <v>279077734548</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>135</v>
       </c>
@@ -16163,7 +16265,7 @@
         <v>91075669292</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>135</v>
       </c>
@@ -16213,7 +16315,7 @@
         <v>135710808032</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>136</v>
       </c>
@@ -16260,7 +16362,7 @@
         <v>109465948.66826923</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>934</v>
       </c>
@@ -16319,7 +16421,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>138</v>
       </c>
@@ -16378,7 +16480,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="93" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>138</v>
       </c>
@@ -16437,7 +16539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>141</v>
       </c>
@@ -16490,7 +16592,7 @@
         <v>33.1</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>141</v>
       </c>
@@ -16543,7 +16645,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>141</v>
       </c>
@@ -16596,7 +16698,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="97" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A97" t="s">
         <v>143</v>
       </c>
@@ -16652,7 +16754,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A98" t="s">
         <v>143</v>
       </c>
@@ -16705,7 +16807,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="99" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A99" t="s">
         <v>143</v>
       </c>
@@ -16758,7 +16860,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="100" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A100" t="s">
         <v>143</v>
       </c>
@@ -16811,7 +16913,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="101" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A101" t="s">
         <v>143</v>
       </c>
@@ -16864,7 +16966,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="102" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A102" t="s">
         <v>143</v>
       </c>
@@ -16917,7 +17019,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="103" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A103" t="s">
         <v>629</v>
       </c>
@@ -16967,7 +17069,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="104" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A104" t="s">
         <v>629</v>
       </c>
@@ -17017,7 +17119,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A105" t="s">
         <v>629</v>
       </c>
@@ -17067,7 +17169,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="106" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -17123,7 +17225,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="107" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A107" t="s">
         <v>147</v>
       </c>
@@ -17179,7 +17281,7 @@
         <v>94.2</v>
       </c>
     </row>
-    <row r="108" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A108" t="s">
         <v>147</v>
       </c>
@@ -17229,7 +17331,7 @@
         <v>98.1</v>
       </c>
     </row>
-    <row r="109" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A109" t="s">
         <v>147</v>
       </c>
@@ -17279,7 +17381,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="110" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A110" t="s">
         <v>147</v>
       </c>
@@ -17329,7 +17431,7 @@
         <v>97.3</v>
       </c>
     </row>
-    <row r="111" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -17379,7 +17481,7 @@
         <v>92.9</v>
       </c>
     </row>
-    <row r="112" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:44" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -17429,7 +17531,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="113" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A113" t="s">
         <v>147</v>
       </c>
@@ -17479,7 +17581,7 @@
         <v>96.7</v>
       </c>
     </row>
-    <row r="114" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A114" t="s">
         <v>147</v>
       </c>
@@ -17529,7 +17631,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="115" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A115" t="s">
         <v>148</v>
       </c>
@@ -17591,7 +17693,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="116" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A116" t="s">
         <v>148</v>
       </c>
@@ -17641,7 +17743,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="117" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A117" t="s">
         <v>148</v>
       </c>
@@ -17691,7 +17793,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A118" t="s">
         <v>148</v>
       </c>
@@ -17750,7 +17852,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A119" t="s">
         <v>148</v>
       </c>
@@ -17809,7 +17911,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="120" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -17868,7 +17970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A121" t="s">
         <v>148</v>
       </c>
@@ -17927,7 +18029,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="122" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A122" t="s">
         <v>148</v>
       </c>
@@ -17986,7 +18088,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="123" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A123" t="s">
         <v>148</v>
       </c>
@@ -18045,7 +18147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A124" t="s">
         <v>148</v>
       </c>
@@ -18104,7 +18206,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="125" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A125" t="s">
         <v>150</v>
       </c>
@@ -18163,7 +18265,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A126" t="s">
         <v>150</v>
       </c>
@@ -18219,7 +18321,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A127" t="s">
         <v>150</v>
       </c>
@@ -18275,7 +18377,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A128" t="s">
         <v>150</v>
       </c>
@@ -18331,7 +18433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A129" t="s">
         <v>150</v>
       </c>
@@ -18387,7 +18489,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A130" t="s">
         <v>152</v>
       </c>
@@ -18434,7 +18536,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="131" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A131" t="s">
         <v>154</v>
       </c>
@@ -18496,7 +18598,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A132" t="s">
         <v>156</v>
       </c>
@@ -18552,7 +18654,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="133" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A133" t="s">
         <v>838</v>
       </c>
@@ -18602,7 +18704,7 @@
         <v>11532788</v>
       </c>
     </row>
-    <row r="134" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A134" t="s">
         <v>640</v>
       </c>
@@ -18667,7 +18769,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="135" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A135" t="s">
         <v>640</v>
       </c>
@@ -18732,7 +18834,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="136" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A136" t="s">
         <v>982</v>
       </c>
@@ -18779,7 +18881,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="137" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A137" t="s">
         <v>158</v>
       </c>
@@ -18853,7 +18955,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="138" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A138" t="s">
         <v>158</v>
       </c>
@@ -18927,7 +19029,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="139" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A139" t="s">
         <v>160</v>
       </c>
@@ -18983,7 +19085,7 @@
         <v>73.7</v>
       </c>
     </row>
-    <row r="140" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A140" t="s">
         <v>160</v>
       </c>
@@ -19036,7 +19138,7 @@
         <v>72.3</v>
       </c>
     </row>
-    <row r="141" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A141" t="s">
         <v>160</v>
       </c>
@@ -19089,7 +19191,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="142" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A142" t="s">
         <v>649</v>
       </c>
@@ -19142,7 +19244,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="143" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A143" t="s">
         <v>649</v>
       </c>
@@ -19192,7 +19294,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="144" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A144" t="s">
         <v>649</v>
       </c>
@@ -19242,7 +19344,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="145" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A145" t="s">
         <v>984</v>
       </c>
@@ -19292,7 +19394,7 @@
         <v>53.7</v>
       </c>
     </row>
-    <row r="146" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A146" t="s">
         <v>976</v>
       </c>
@@ -19339,7 +19441,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="147" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -19389,7 +19491,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="148" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A148" t="s">
         <v>166</v>
       </c>
@@ -19442,7 +19544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A149" t="s">
         <v>166</v>
       </c>
@@ -19495,7 +19597,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="150" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A150" t="s">
         <v>167</v>
       </c>
@@ -19560,7 +19662,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="151" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A151" t="s">
         <v>167</v>
       </c>
@@ -19610,7 +19712,7 @@
         <v>98.7</v>
       </c>
     </row>
-    <row r="152" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A152" t="s">
         <v>167</v>
       </c>
@@ -19660,7 +19762,7 @@
         <v>99.3</v>
       </c>
     </row>
-    <row r="153" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A153" t="s">
         <v>167</v>
       </c>
@@ -19710,7 +19812,7 @@
         <v>93.8</v>
       </c>
     </row>
-    <row r="154" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A154" t="s">
         <v>167</v>
       </c>
@@ -19757,7 +19859,7 @@
         <v>93.1</v>
       </c>
     </row>
-    <row r="155" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A155" t="s">
         <v>167</v>
       </c>
@@ -19804,7 +19906,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="156" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A156" t="s">
         <v>167</v>
       </c>
@@ -19854,7 +19956,7 @@
         <v>98.8</v>
       </c>
     </row>
-    <row r="157" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A157" t="s">
         <v>167</v>
       </c>
@@ -19901,7 +20003,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="158" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A158" t="s">
         <v>167</v>
       </c>
@@ -19948,7 +20050,7 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="159" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -19995,7 +20097,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="160" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A160" t="s">
         <v>161</v>
       </c>
@@ -20003,7 +20105,7 @@
         <v>165</v>
       </c>
       <c r="C160" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="D160" t="s">
         <v>89</v>
@@ -20042,7 +20144,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="161" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A161" t="s">
         <v>161</v>
       </c>
@@ -20089,7 +20191,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="162" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A162" t="s">
         <v>161</v>
       </c>
@@ -20136,7 +20238,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="163" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A163" t="s">
         <v>168</v>
       </c>
@@ -20183,7 +20285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A164" t="s">
         <v>168</v>
       </c>
@@ -20236,7 +20338,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="165" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -20289,7 +20391,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -20342,7 +20444,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="167" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A167" t="s">
         <v>168</v>
       </c>
@@ -20395,7 +20497,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A168" t="s">
         <v>168</v>
       </c>
@@ -20448,7 +20550,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="169" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A169" t="s">
         <v>168</v>
       </c>
@@ -20501,7 +20603,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="170" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -20554,7 +20656,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="171" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A171" t="s">
         <v>168</v>
       </c>
@@ -20607,7 +20709,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="172" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A172" t="s">
         <v>168</v>
       </c>
@@ -20660,7 +20762,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A173" t="s">
         <v>168</v>
       </c>
@@ -20713,7 +20815,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="174" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A174" t="s">
         <v>168</v>
       </c>
@@ -20766,7 +20868,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="175" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A175" t="s">
         <v>168</v>
       </c>
@@ -20819,7 +20921,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="176" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:39" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A176" t="s">
         <v>666</v>
       </c>
@@ -20866,7 +20968,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="177" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A177" t="s">
         <v>666</v>
       </c>
@@ -20913,7 +21015,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="178" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A178" t="s">
         <v>666</v>
       </c>
@@ -20960,7 +21062,7 @@
         <v>54.9</v>
       </c>
     </row>
-    <row r="179" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A179" t="s">
         <v>666</v>
       </c>
@@ -21010,7 +21112,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="180" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A180" t="s">
         <v>666</v>
       </c>
@@ -21060,7 +21162,7 @@
         <v>56.4</v>
       </c>
     </row>
-    <row r="181" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A181" t="s">
         <v>666</v>
       </c>
@@ -21107,7 +21209,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="182" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A182" t="s">
         <v>666</v>
       </c>
@@ -21157,7 +21259,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="183" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A183" t="s">
         <v>666</v>
       </c>
@@ -21207,7 +21309,7 @@
         <v>41.3</v>
       </c>
     </row>
-    <row r="184" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A184" t="s">
         <v>666</v>
       </c>
@@ -21254,7 +21356,7 @@
         <v>44.1</v>
       </c>
     </row>
-    <row r="185" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A185" t="s">
         <v>666</v>
       </c>
@@ -21301,7 +21403,7 @@
         <v>38.299999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A186" t="s">
         <v>182</v>
       </c>
@@ -21354,7 +21456,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="187" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A187" t="s">
         <v>182</v>
       </c>
@@ -21410,7 +21512,7 @@
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="188" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A188" t="s">
         <v>182</v>
       </c>
@@ -21466,7 +21568,7 @@
         <v>77.900000000000006</v>
       </c>
     </row>
-    <row r="189" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A189" t="s">
         <v>182</v>
       </c>
@@ -21519,7 +21621,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="190" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A190" t="s">
         <v>182</v>
       </c>
@@ -21575,7 +21677,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="191" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A191" t="s">
         <v>182</v>
       </c>
@@ -21631,7 +21733,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="192" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:42" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A192" t="s">
         <v>182</v>
       </c>
@@ -21684,7 +21786,7 @@
         <v>95.4</v>
       </c>
     </row>
-    <row r="193" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A193" t="s">
         <v>182</v>
       </c>
@@ -21740,7 +21842,7 @@
         <v>95.3</v>
       </c>
     </row>
-    <row r="194" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A194" t="s">
         <v>182</v>
       </c>
@@ -21796,7 +21898,7 @@
         <v>95.8</v>
       </c>
     </row>
-    <row r="195" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A195" t="s">
         <v>182</v>
       </c>
@@ -21849,7 +21951,7 @@
         <v>94.4</v>
       </c>
     </row>
-    <row r="196" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A196" t="s">
         <v>182</v>
       </c>
@@ -21905,7 +22007,7 @@
         <v>93.2</v>
       </c>
     </row>
-    <row r="197" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A197" t="s">
         <v>182</v>
       </c>
@@ -21961,7 +22063,7 @@
         <v>95.8</v>
       </c>
     </row>
-    <row r="198" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A198" t="s">
         <v>182</v>
       </c>
@@ -22014,7 +22116,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="199" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A199" t="s">
         <v>188</v>
       </c>
@@ -22067,7 +22169,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="200" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A200" t="s">
         <v>188</v>
       </c>
@@ -22132,7 +22234,7 @@
         <v>83.4</v>
       </c>
     </row>
-    <row r="201" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A201" t="s">
         <v>188</v>
       </c>
@@ -22197,7 +22299,7 @@
         <v>85.4</v>
       </c>
     </row>
-    <row r="202" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A202" t="s">
         <v>189</v>
       </c>
@@ -22256,7 +22358,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="203" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A203" t="s">
         <v>189</v>
       </c>
@@ -22318,7 +22420,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="204" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A204" t="s">
         <v>189</v>
       </c>
@@ -22380,7 +22482,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="205" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A205" t="s">
         <v>190</v>
       </c>
@@ -22430,7 +22532,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="206" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A206" t="s">
         <v>190</v>
       </c>
@@ -22480,7 +22582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A207" t="s">
         <v>190</v>
       </c>
@@ -22530,7 +22632,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="208" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A208" t="s">
         <v>190</v>
       </c>
@@ -22580,7 +22682,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="209" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A209" t="s">
         <v>190</v>
       </c>
@@ -22630,7 +22732,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="210" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A210" t="s">
         <v>190</v>
       </c>
@@ -22680,7 +22782,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="211" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A211" t="s">
         <v>190</v>
       </c>
@@ -22730,7 +22832,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="212" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A212" t="s">
         <v>190</v>
       </c>
@@ -22780,7 +22882,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="213" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A213" t="s">
         <v>190</v>
       </c>
@@ -22830,7 +22932,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="214" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A214" t="s">
         <v>190</v>
       </c>
@@ -22880,7 +22982,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="215" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A215" t="s">
         <v>190</v>
       </c>
@@ -22930,7 +23032,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="216" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A216" t="s">
         <v>190</v>
       </c>
@@ -22980,7 +23082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A217" t="s">
         <v>190</v>
       </c>
@@ -23030,7 +23132,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="218" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A218" t="s">
         <v>190</v>
       </c>
@@ -23080,7 +23182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="219" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A219" t="s">
         <v>190</v>
       </c>
@@ -23130,7 +23232,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="220" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A220" t="s">
         <v>190</v>
       </c>
@@ -23180,7 +23282,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="221" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A221" t="s">
         <v>190</v>
       </c>
@@ -23230,7 +23332,7 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="222" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A222" t="s">
         <v>190</v>
       </c>
@@ -23280,7 +23382,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="223" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A223" t="s">
         <v>190</v>
       </c>
@@ -23330,7 +23432,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="224" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A224" t="s">
         <v>190</v>
       </c>
@@ -23380,7 +23482,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="225" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -23430,7 +23532,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="226" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A226" t="s">
         <v>190</v>
       </c>
@@ -23480,7 +23582,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="227" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A227" t="s">
         <v>190</v>
       </c>
@@ -23530,7 +23632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="228" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -23580,7 +23682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A229" t="s">
         <v>190</v>
       </c>
@@ -23630,7 +23732,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="230" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A230" t="s">
         <v>190</v>
       </c>
@@ -23680,7 +23782,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="231" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A231" t="s">
         <v>190</v>
       </c>
@@ -23730,7 +23832,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="232" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A232" t="s">
         <v>191</v>
       </c>
@@ -23780,7 +23882,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="233" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A233" t="s">
         <v>191</v>
       </c>
@@ -23833,7 +23935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A234" t="s">
         <v>191</v>
       </c>
@@ -23886,7 +23988,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="235" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A235" t="s">
         <v>191</v>
       </c>
@@ -23936,7 +24038,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="236" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A236" t="s">
         <v>191</v>
       </c>
@@ -23989,7 +24091,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="237" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A237" t="s">
         <v>191</v>
       </c>
@@ -24042,7 +24144,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="238" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A238" t="s">
         <v>191</v>
       </c>
@@ -24092,7 +24194,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="239" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A239" t="s">
         <v>191</v>
       </c>
@@ -24145,7 +24247,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="240" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A240" t="s">
         <v>191</v>
       </c>
@@ -24198,7 +24300,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="241" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A241" t="s">
         <v>191</v>
       </c>
@@ -24248,7 +24350,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A242" t="s">
         <v>191</v>
       </c>
@@ -24301,7 +24403,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="243" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A243" t="s">
         <v>191</v>
       </c>
@@ -24354,7 +24456,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A244" t="s">
         <v>191</v>
       </c>
@@ -24404,7 +24506,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="245" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A245" t="s">
         <v>191</v>
       </c>
@@ -24457,7 +24559,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="246" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A246" t="s">
         <v>191</v>
       </c>
@@ -24510,7 +24612,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="247" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A247" t="s">
         <v>191</v>
       </c>
@@ -24560,7 +24662,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="248" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A248" t="s">
         <v>191</v>
       </c>
@@ -24613,7 +24715,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="249" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A249" t="s">
         <v>191</v>
       </c>
@@ -24666,7 +24768,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="250" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A250" t="s">
         <v>191</v>
       </c>
@@ -24716,7 +24818,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="251" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A251" t="s">
         <v>191</v>
       </c>
@@ -24769,7 +24871,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="252" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A252" t="s">
         <v>191</v>
       </c>
@@ -24822,7 +24924,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="253" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A253" t="s">
         <v>191</v>
       </c>
@@ -24872,7 +24974,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="254" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A254" t="s">
         <v>191</v>
       </c>
@@ -24925,7 +25027,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="255" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A255" t="s">
         <v>191</v>
       </c>
@@ -24978,7 +25080,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="256" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A256" t="s">
         <v>191</v>
       </c>
@@ -25028,7 +25130,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="257" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A257" t="s">
         <v>191</v>
       </c>
@@ -25081,7 +25183,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="258" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A258" t="s">
         <v>191</v>
       </c>
@@ -25134,7 +25236,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="259" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A259" t="s">
         <v>191</v>
       </c>
@@ -25184,7 +25286,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="260" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A260" t="s">
         <v>191</v>
       </c>
@@ -25237,7 +25339,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="261" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A261" t="s">
         <v>191</v>
       </c>
@@ -25290,7 +25392,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="262" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A262" t="s">
         <v>191</v>
       </c>
@@ -25340,7 +25442,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="263" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A263" t="s">
         <v>191</v>
       </c>
@@ -25393,7 +25495,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="264" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A264" t="s">
         <v>191</v>
       </c>
@@ -25446,7 +25548,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="265" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A265" t="s">
         <v>191</v>
       </c>
@@ -25490,7 +25592,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="266" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A266" t="s">
         <v>191</v>
       </c>
@@ -25537,7 +25639,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="267" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A267" t="s">
         <v>191</v>
       </c>
@@ -25584,7 +25686,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="268" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A268" t="s">
         <v>194</v>
       </c>
@@ -25628,7 +25730,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="269" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A269" t="s">
         <v>194</v>
       </c>
@@ -25675,7 +25777,7 @@
         <v>84.2</v>
       </c>
     </row>
-    <row r="270" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A270" t="s">
         <v>194</v>
       </c>
@@ -25722,7 +25824,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="271" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A271" t="s">
         <v>194</v>
       </c>
@@ -25766,7 +25868,7 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="272" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A272" t="s">
         <v>194</v>
       </c>
@@ -25813,7 +25915,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="273" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A273" t="s">
         <v>194</v>
       </c>
@@ -25860,7 +25962,7 @@
         <v>84.9</v>
       </c>
     </row>
-    <row r="274" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A274" t="s">
         <v>198</v>
       </c>
@@ -25922,7 +26024,7 @@
         <v>82.1</v>
       </c>
     </row>
-    <row r="275" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A275" t="s">
         <v>198</v>
       </c>
@@ -25984,7 +26086,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="276" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A276" t="s">
         <v>198</v>
       </c>
@@ -26046,7 +26148,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="277" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A277" t="s">
         <v>198</v>
       </c>
@@ -26114,7 +26216,7 @@
         <v>59.4</v>
       </c>
     </row>
-    <row r="278" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A278" t="s">
         <v>198</v>
       </c>
@@ -26176,7 +26278,7 @@
         <v>77.599999999999994</v>
       </c>
     </row>
-    <row r="279" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A279" t="s">
         <v>198</v>
       </c>
@@ -26238,7 +26340,7 @@
         <v>97.9</v>
       </c>
     </row>
-    <row r="280" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A280" t="s">
         <v>198</v>
       </c>
@@ -26300,7 +26402,7 @@
         <v>99.4</v>
       </c>
     </row>
-    <row r="281" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A281" t="s">
         <v>198</v>
       </c>
@@ -26362,7 +26464,7 @@
         <v>93.4</v>
       </c>
     </row>
-    <row r="282" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A282" t="s">
         <v>198</v>
       </c>
@@ -26424,7 +26526,7 @@
         <v>93.6</v>
       </c>
     </row>
-    <row r="283" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A283" t="s">
         <v>198</v>
       </c>
@@ -26483,7 +26585,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="284" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A284" t="s">
         <v>198</v>
       </c>
@@ -26545,7 +26647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="285" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A285" t="s">
         <v>198</v>
       </c>
@@ -26607,7 +26709,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="286" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A286" t="s">
         <v>198</v>
       </c>
@@ -26669,7 +26771,7 @@
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="287" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A287" t="s">
         <v>198</v>
       </c>
@@ -26731,7 +26833,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="288" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A288" t="s">
         <v>198</v>
       </c>
@@ -26793,7 +26895,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="289" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A289" t="s">
         <v>198</v>
       </c>
@@ -26855,7 +26957,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="290" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A290" t="s">
         <v>199</v>
       </c>
@@ -26920,7 +27022,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="291" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A291" t="s">
         <v>199</v>
       </c>
@@ -26988,7 +27090,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="292" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A292" t="s">
         <v>199</v>
       </c>
@@ -27056,7 +27158,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="293" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A293" t="s">
         <v>199</v>
       </c>
@@ -27121,7 +27223,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="294" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A294" t="s">
         <v>199</v>
       </c>
@@ -27189,7 +27291,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="295" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A295" t="s">
         <v>199</v>
       </c>
@@ -27257,7 +27359,7 @@
         <v>69.3</v>
       </c>
     </row>
-    <row r="296" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A296" t="s">
         <v>199</v>
       </c>
@@ -27322,7 +27424,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="297" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A297" t="s">
         <v>199</v>
       </c>
@@ -27390,7 +27492,7 @@
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="298" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A298" t="s">
         <v>199</v>
       </c>
@@ -27458,7 +27560,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="299" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A299" t="s">
         <v>200</v>
       </c>
@@ -27508,7 +27610,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="300" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A300" t="s">
         <v>200</v>
       </c>
@@ -27558,7 +27660,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="301" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A301" t="s">
         <v>200</v>
       </c>
@@ -27608,7 +27710,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="302" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A302" t="s">
         <v>688</v>
       </c>
@@ -27655,7 +27757,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="303" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A303" t="s">
         <v>201</v>
       </c>
@@ -27708,7 +27810,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="304" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A304" t="s">
         <v>201</v>
       </c>
@@ -27761,7 +27863,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="305" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A305" t="s">
         <v>202</v>
       </c>
@@ -27823,7 +27925,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="306" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A306" t="s">
         <v>202</v>
       </c>
@@ -27888,7 +27990,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="307" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A307" t="s">
         <v>202</v>
       </c>
@@ -27953,7 +28055,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="308" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A308" t="s">
         <v>52</v>
       </c>
@@ -28024,7 +28126,7 @@
         <v>63.75</v>
       </c>
     </row>
-    <row r="309" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A309" t="s">
         <v>52</v>
       </c>
@@ -28095,7 +28197,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="310" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A310" t="s">
         <v>52</v>
       </c>
@@ -28148,7 +28250,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A311" t="s">
         <v>52</v>
       </c>
@@ -28204,7 +28306,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="312" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A312" t="s">
         <v>52</v>
       </c>
@@ -28254,7 +28356,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="313" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A313" t="s">
         <v>52</v>
       </c>
@@ -28304,7 +28406,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="314" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A314" t="s">
         <v>52</v>
       </c>
@@ -28360,7 +28462,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="315" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A315" t="s">
         <v>52</v>
       </c>
@@ -28410,7 +28512,7 @@
         <v>42.7</v>
       </c>
     </row>
-    <row r="316" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A316" t="s">
         <v>52</v>
       </c>
@@ -28460,7 +28562,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="317" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A317" t="s">
         <v>52</v>
       </c>
@@ -28513,7 +28615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A318" t="s">
         <v>52</v>
       </c>
@@ -28566,7 +28668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="319" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A319" t="s">
         <v>52</v>
       </c>
@@ -28619,7 +28721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="320" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A320" t="s">
         <v>203</v>
       </c>
@@ -28684,7 +28786,7 @@
         <v>39.6</v>
       </c>
     </row>
-    <row r="321" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A321" t="s">
         <v>692</v>
       </c>
@@ -28731,7 +28833,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="322" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A322" t="s">
         <v>696</v>
       </c>
@@ -28778,7 +28880,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="323" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A323" t="s">
         <v>696</v>
       </c>
@@ -28825,7 +28927,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="324" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A324" t="s">
         <v>696</v>
       </c>
@@ -28869,7 +28971,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="325" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A325" t="s">
         <v>205</v>
       </c>
@@ -28922,7 +29024,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="326" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A326" t="s">
         <v>205</v>
       </c>
@@ -28978,7 +29080,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="327" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A327" t="s">
         <v>205</v>
       </c>
@@ -29034,7 +29136,7 @@
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="328" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A328" t="s">
         <v>207</v>
       </c>
@@ -29087,7 +29189,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="329" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A329" t="s">
         <v>207</v>
       </c>
@@ -29146,7 +29248,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="330" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A330" t="s">
         <v>207</v>
       </c>
@@ -29205,7 +29307,7 @@
         <v>76.7</v>
       </c>
     </row>
-    <row r="331" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A331" t="s">
         <v>208</v>
       </c>
@@ -29258,7 +29360,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="332" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A332" t="s">
         <v>209</v>
       </c>
@@ -29308,7 +29410,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="333" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A333" t="s">
         <v>708</v>
       </c>
@@ -29352,7 +29454,7 @@
         <v>12.87</v>
       </c>
     </row>
-    <row r="334" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A334" t="s">
         <v>714</v>
       </c>
@@ -29399,7 +29501,7 @@
         <v>11.17</v>
       </c>
     </row>
-    <row r="335" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A335" t="s">
         <v>716</v>
       </c>
@@ -29446,7 +29548,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="336" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A336" t="s">
         <v>211</v>
       </c>
@@ -29490,7 +29592,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="337" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A337" t="s">
         <v>722</v>
       </c>
@@ -29534,7 +29636,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="338" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A338" t="s">
         <v>977</v>
       </c>
@@ -29620,7 +29722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A339" t="s">
         <v>212</v>
       </c>
@@ -29679,7 +29781,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="340" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A340" t="s">
         <v>214</v>
       </c>
@@ -29729,7 +29831,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="341" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A341" t="s">
         <v>214</v>
       </c>
@@ -29779,7 +29881,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="342" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A342" t="s">
         <v>214</v>
       </c>
@@ -29829,7 +29931,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="343" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A343" t="s">
         <v>216</v>
       </c>
@@ -29879,7 +29981,7 @@
         <v>62.3</v>
       </c>
     </row>
-    <row r="344" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A344" t="s">
         <v>880</v>
       </c>
@@ -29926,7 +30028,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="345" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A345" t="s">
         <v>217</v>
       </c>
@@ -30039,7 +30141,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="346" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A346" t="s">
         <v>219</v>
       </c>
@@ -30098,7 +30200,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="347" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A347" t="s">
         <v>221</v>
       </c>
@@ -30163,7 +30265,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="348" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A348" t="s">
         <v>221</v>
       </c>
@@ -30228,7 +30330,7 @@
         <v>63.3</v>
       </c>
     </row>
-    <row r="349" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A349" t="s">
         <v>221</v>
       </c>
@@ -30293,7 +30395,7 @@
         <v>36.700000000000003</v>
       </c>
     </row>
-    <row r="350" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A350" t="s">
         <v>222</v>
       </c>
@@ -30358,7 +30460,7 @@
         <v>3496.2608515765401</v>
       </c>
     </row>
-    <row r="351" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A351" t="s">
         <v>222</v>
       </c>
@@ -30423,7 +30525,7 @@
         <v>1226.3508710219101</v>
       </c>
     </row>
-    <row r="352" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A352" t="s">
         <v>222</v>
       </c>
@@ -30488,7 +30590,7 @@
         <v>1725.7948292896101</v>
       </c>
     </row>
-    <row r="353" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A353" t="s">
         <v>222</v>
       </c>
@@ -30553,7 +30655,7 @@
         <v>968.82600160885897</v>
       </c>
     </row>
-    <row r="354" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A354" t="s">
         <v>222</v>
       </c>
@@ -30618,7 +30720,7 @@
         <v>421.882384363715</v>
       </c>
     </row>
-    <row r="355" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A355" t="s">
         <v>222</v>
       </c>
@@ -30683,7 +30785,7 @@
         <v>342.49926488570702</v>
       </c>
     </row>
-    <row r="356" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A356" t="s">
         <v>222</v>
       </c>
@@ -30748,7 +30850,7 @@
         <v>755.93852910636303</v>
       </c>
     </row>
-    <row r="357" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A357" t="s">
         <v>222</v>
       </c>
@@ -30813,7 +30915,7 @@
         <v>780.86317256477196</v>
       </c>
     </row>
-    <row r="358" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A358" t="s">
         <v>222</v>
       </c>
@@ -30878,7 +30980,7 @@
         <v>252.54846263087501</v>
       </c>
     </row>
-    <row r="359" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A359" t="s">
         <v>223</v>
       </c>
@@ -30946,7 +31048,7 @@
         <v>14.93</v>
       </c>
     </row>
-    <row r="360" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A360" t="s">
         <v>223</v>
       </c>
@@ -31017,7 +31119,7 @@
         <v>12.57</v>
       </c>
     </row>
-    <row r="361" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A361" t="s">
         <v>223</v>
       </c>
@@ -31088,7 +31190,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A362" t="s">
         <v>223</v>
       </c>
@@ -31153,7 +31255,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="363" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A363" t="s">
         <v>226</v>
       </c>
@@ -31218,7 +31320,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="364" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A364" t="s">
         <v>226</v>
       </c>
@@ -31283,7 +31385,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="365" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A365" t="s">
         <v>227</v>
       </c>
@@ -31336,7 +31438,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="366" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A366" t="s">
         <v>227</v>
       </c>
@@ -31392,7 +31494,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="367" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A367" t="s">
         <v>227</v>
       </c>
@@ -31448,7 +31550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A368" t="s">
         <v>727</v>
       </c>
@@ -31495,7 +31597,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="369" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A369" t="s">
         <v>727</v>
       </c>
@@ -31545,7 +31647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="370" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A370" t="s">
         <v>727</v>
       </c>
@@ -31595,7 +31697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A371" t="s">
         <v>727</v>
       </c>
@@ -31642,7 +31744,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="372" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A372" t="s">
         <v>727</v>
       </c>
@@ -31692,7 +31794,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="373" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A373" t="s">
         <v>727</v>
       </c>
@@ -31742,7 +31844,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="374" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A374" t="s">
         <v>883</v>
       </c>
@@ -31804,7 +31906,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="375" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A375" t="s">
         <v>734</v>
       </c>
@@ -31857,7 +31959,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="376" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A376" t="s">
         <v>230</v>
       </c>
@@ -31925,7 +32027,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="377" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A377" t="s">
         <v>230</v>
       </c>
@@ -31981,7 +32083,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="378" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A378" t="s">
         <v>231</v>
       </c>
@@ -32037,7 +32139,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="379" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A379" t="s">
         <v>232</v>
       </c>
@@ -32084,7 +32186,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="380" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A380" t="s">
         <v>743</v>
       </c>
@@ -32149,7 +32251,7 @@
         <v>173.59</v>
       </c>
     </row>
-    <row r="381" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A381" t="s">
         <v>743</v>
       </c>
@@ -32214,7 +32316,7 @@
         <v>11176.73</v>
       </c>
     </row>
-    <row r="382" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A382" t="s">
         <v>743</v>
       </c>
@@ -32285,7 +32387,7 @@
         <v>788386</v>
       </c>
     </row>
-    <row r="383" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A383" t="s">
         <v>234</v>
       </c>
@@ -32398,7 +32500,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A384" t="s">
         <v>235</v>
       </c>
@@ -32463,7 +32565,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="385" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A385" t="s">
         <v>890</v>
       </c>
@@ -32567,7 +32669,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A386" t="s">
         <v>895</v>
       </c>
@@ -32617,7 +32719,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="387" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A387" t="s">
         <v>902</v>
       </c>
@@ -32673,7 +32775,7 @@
         <v>58.763199999999998</v>
       </c>
     </row>
-    <row r="388" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A388" t="s">
         <v>237</v>
       </c>
@@ -32732,7 +32834,7 @@
         <v>99.92</v>
       </c>
     </row>
-    <row r="389" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A389" t="s">
         <v>237</v>
       </c>
@@ -32791,7 +32893,7 @@
         <v>93.37</v>
       </c>
     </row>
-    <row r="390" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A390" t="s">
         <v>237</v>
       </c>
@@ -32847,7 +32949,7 @@
         <v>98.2</v>
       </c>
     </row>
-    <row r="391" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A391" t="s">
         <v>910</v>
       </c>
@@ -32900,7 +33002,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="392" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A392" t="s">
         <v>906</v>
       </c>
@@ -32968,7 +33070,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="393" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A393" t="s">
         <v>751</v>
       </c>
@@ -33030,7 +33132,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="394" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A394" t="s">
         <v>751</v>
       </c>
@@ -33092,7 +33194,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="395" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A395" t="s">
         <v>751</v>
       </c>
@@ -33148,7 +33250,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="396" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A396" t="s">
         <v>751</v>
       </c>
@@ -33204,7 +33306,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="397" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A397" t="s">
         <v>751</v>
       </c>
@@ -33257,7 +33359,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="398" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A398" t="s">
         <v>751</v>
       </c>
@@ -33313,7 +33415,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="399" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A399" t="s">
         <v>751</v>
       </c>
@@ -33366,7 +33468,7 @@
         <v>-4.7</v>
       </c>
     </row>
-    <row r="400" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A400" t="s">
         <v>768</v>
       </c>
@@ -33416,7 +33518,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="401" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A401" t="s">
         <v>238</v>
       </c>
@@ -33472,7 +33574,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="402" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A402" t="s">
         <v>930</v>
       </c>
@@ -33504,7 +33606,7 @@
         <v>967</v>
       </c>
       <c r="P402" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="R402" t="s">
         <v>89</v>
@@ -33540,7 +33642,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="403" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A403" t="s">
         <v>930</v>
       </c>
@@ -33572,7 +33674,7 @@
         <v>967</v>
       </c>
       <c r="P403" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="R403" t="s">
         <v>89</v>
@@ -33608,7 +33710,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="404" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A404" t="s">
         <v>772</v>
       </c>
@@ -33616,7 +33718,7 @@
         <v>939</v>
       </c>
       <c r="C404" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D404" t="s">
         <v>89</v>
@@ -33670,7 +33772,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="405" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A405" t="s">
         <v>772</v>
       </c>
@@ -33678,7 +33780,7 @@
         <v>939</v>
       </c>
       <c r="C405" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="D405" t="s">
         <v>89</v>
@@ -33732,7 +33834,7 @@
         <v>1355.3</v>
       </c>
     </row>
-    <row r="406" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A406" t="s">
         <v>772</v>
       </c>
@@ -33740,7 +33842,7 @@
         <v>939</v>
       </c>
       <c r="C406" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="D406" t="s">
         <v>89</v>
@@ -33794,7 +33896,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="407" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A407" t="s">
         <v>772</v>
       </c>
@@ -33802,7 +33904,7 @@
         <v>939</v>
       </c>
       <c r="C407" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="D407" t="s">
         <v>89</v>
@@ -33856,7 +33958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A408" t="s">
         <v>772</v>
       </c>
@@ -33864,7 +33966,7 @@
         <v>939</v>
       </c>
       <c r="C408" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="D408" t="s">
         <v>89</v>
@@ -33918,7 +34020,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="409" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A409" t="s">
         <v>772</v>
       </c>
@@ -33926,7 +34028,7 @@
         <v>939</v>
       </c>
       <c r="C409" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="D409" t="s">
         <v>89</v>
@@ -33980,7 +34082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="410" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A410" t="s">
         <v>772</v>
       </c>
@@ -33988,7 +34090,7 @@
         <v>939</v>
       </c>
       <c r="C410" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="D410" t="s">
         <v>89</v>
@@ -34042,7 +34144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="411" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A411" t="s">
         <v>772</v>
       </c>
@@ -34050,7 +34152,7 @@
         <v>939</v>
       </c>
       <c r="C411" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="D411" t="s">
         <v>89</v>
@@ -34104,7 +34206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A412" t="s">
         <v>772</v>
       </c>
@@ -34112,7 +34214,7 @@
         <v>939</v>
       </c>
       <c r="C412" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="D412" t="s">
         <v>89</v>
@@ -34163,7 +34265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A413" t="s">
         <v>772</v>
       </c>
@@ -34171,7 +34273,7 @@
         <v>939</v>
       </c>
       <c r="C413" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="D413" t="s">
         <v>89</v>
@@ -34222,7 +34324,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A414" t="s">
         <v>772</v>
       </c>
@@ -34230,7 +34332,7 @@
         <v>939</v>
       </c>
       <c r="C414" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="D414" t="s">
         <v>89</v>
@@ -34278,7 +34380,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="415" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A415" t="s">
         <v>772</v>
       </c>
@@ -34286,7 +34388,7 @@
         <v>939</v>
       </c>
       <c r="C415" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="D415" t="s">
         <v>89</v>
@@ -34337,7 +34439,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="416" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A416" t="s">
         <v>772</v>
       </c>
@@ -34345,7 +34447,7 @@
         <v>939</v>
       </c>
       <c r="C416" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="D416" t="s">
         <v>89</v>
@@ -34396,7 +34498,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="417" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A417" t="s">
         <v>772</v>
       </c>
@@ -34404,7 +34506,7 @@
         <v>939</v>
       </c>
       <c r="C417" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D417" t="s">
         <v>89</v>
@@ -34455,7 +34557,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="418" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A418" t="s">
         <v>986</v>
       </c>
@@ -34517,15 +34619,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="419" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A419" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B419" t="s">
         <v>131</v>
       </c>
       <c r="C419" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="D419" t="s">
         <v>89</v>
@@ -34549,7 +34651,7 @@
         <v>967</v>
       </c>
       <c r="P419" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="R419" t="s">
         <v>89</v>
@@ -34585,15 +34687,15 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="420" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A420" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B420" t="s">
         <v>131</v>
       </c>
       <c r="C420" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D420" t="s">
         <v>89</v>
@@ -34617,7 +34719,7 @@
         <v>967</v>
       </c>
       <c r="P420" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="R420" t="s">
         <v>89</v>
@@ -34653,15 +34755,15 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="421" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A421" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B421" t="s">
         <v>134</v>
       </c>
       <c r="C421" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="D421" t="s">
         <v>89</v>
@@ -34715,7 +34817,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="422" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A422" t="s">
         <v>69</v>
       </c>
@@ -34762,7 +34864,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="423" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A423" t="s">
         <v>69</v>
       </c>
@@ -34812,7 +34914,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="424" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A424" t="s">
         <v>69</v>
       </c>
@@ -34862,7 +34964,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="425" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A425" t="s">
         <v>69</v>
       </c>
@@ -34912,7 +35014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="426" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A426" t="s">
         <v>69</v>
       </c>
@@ -34962,7 +35064,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="427" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A427" t="s">
         <v>69</v>
       </c>
@@ -35012,7 +35114,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="428" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A428" t="s">
         <v>69</v>
       </c>
@@ -35062,7 +35164,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="429" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A429" t="s">
         <v>69</v>
       </c>
@@ -35112,7 +35214,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="430" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A430" t="s">
         <v>69</v>
       </c>
@@ -35162,7 +35264,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="431" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A431" t="s">
         <v>69</v>
       </c>
@@ -35212,7 +35314,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="432" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A432" t="s">
         <v>69</v>
       </c>
@@ -35262,7 +35364,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="433" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A433" t="s">
         <v>69</v>
       </c>
@@ -35312,7 +35414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="434" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A434" t="s">
         <v>69</v>
       </c>
@@ -35362,7 +35464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="435" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A435" t="s">
         <v>69</v>
       </c>
@@ -35412,7 +35514,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="436" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A436" t="s">
         <v>69</v>
       </c>
@@ -35462,7 +35564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="437" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A437" t="s">
         <v>69</v>
       </c>
@@ -35512,7 +35614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="438" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A438" t="s">
         <v>69</v>
       </c>
@@ -35562,7 +35664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="439" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A439" t="s">
         <v>69</v>
       </c>
@@ -35612,7 +35714,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A440" t="s">
         <v>69</v>
       </c>
@@ -35662,7 +35764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A441" t="s">
         <v>69</v>
       </c>
@@ -35712,7 +35814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="442" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A442" t="s">
         <v>69</v>
       </c>
@@ -35762,7 +35864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="443" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A443" t="s">
         <v>69</v>
       </c>
@@ -35812,7 +35914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A444" t="s">
         <v>69</v>
       </c>
@@ -35862,7 +35964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="445" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A445" t="s">
         <v>69</v>
       </c>
@@ -35912,7 +36014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="446" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A446" t="s">
         <v>69</v>
       </c>
@@ -35962,7 +36064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="447" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A447" t="s">
         <v>69</v>
       </c>
@@ -36012,7 +36114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="448" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:41" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A448" t="s">
         <v>69</v>
       </c>
@@ -36062,7 +36164,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="449" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A449" t="s">
         <v>69</v>
       </c>
@@ -36112,7 +36214,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="450" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A450" t="s">
         <v>69</v>
       </c>
@@ -36162,7 +36264,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="451" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A451" t="s">
         <v>69</v>
       </c>
@@ -36212,7 +36314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="452" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A452" t="s">
         <v>69</v>
       </c>
@@ -36262,7 +36364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="453" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A453" t="s">
         <v>773</v>
       </c>
@@ -36312,7 +36414,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="454" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A454" t="s">
         <v>928</v>
       </c>
@@ -36362,7 +36464,7 @@
         <v>38.450000000000003</v>
       </c>
     </row>
-    <row r="455" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A455" t="s">
         <v>777</v>
       </c>
@@ -36409,7 +36511,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="456" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A456" t="s">
         <v>855</v>
       </c>
@@ -36465,7 +36567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A457" t="s">
         <v>239</v>
       </c>
@@ -36530,7 +36632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="458" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A458" t="s">
         <v>241</v>
       </c>
@@ -36580,7 +36682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="459" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A459" t="s">
         <v>241</v>
       </c>
@@ -36630,7 +36732,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="460" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A460" t="s">
         <v>241</v>
       </c>
@@ -36680,7 +36782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A461" t="s">
         <v>241</v>
       </c>
@@ -36730,7 +36832,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="462" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A462" t="s">
         <v>242</v>
       </c>
@@ -36798,7 +36900,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="463" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A463" t="s">
         <v>929</v>
       </c>
@@ -36854,7 +36956,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="464" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A464" t="s">
         <v>244</v>
       </c>
@@ -36916,7 +37018,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="465" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A465" t="s">
         <v>244</v>
       </c>
@@ -36978,7 +37080,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="466" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A466" t="s">
         <v>244</v>
       </c>
@@ -37028,7 +37130,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="467" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A467" t="s">
         <v>244</v>
       </c>
@@ -37072,7 +37174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A468" t="s">
         <v>244</v>
       </c>
@@ -37122,7 +37224,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="469" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A469" t="s">
         <v>931</v>
       </c>
@@ -37172,7 +37274,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="470" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A470" t="s">
         <v>931</v>
       </c>
@@ -37222,7 +37324,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="471" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A471" t="s">
         <v>980</v>
       </c>
@@ -37272,7 +37374,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="472" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A472" t="s">
         <v>245</v>
       </c>
@@ -37337,7 +37439,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="473" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A473" t="s">
         <v>245</v>
       </c>
@@ -37399,7 +37501,7 @@
         <v>12239</v>
       </c>
     </row>
-    <row r="474" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A474" t="s">
         <v>247</v>
       </c>
@@ -37470,7 +37572,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="475" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A475" t="s">
         <v>793</v>
       </c>
@@ -37526,7 +37628,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="476" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A476" t="s">
         <v>797</v>
       </c>
@@ -37576,7 +37678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="477" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A477" t="s">
         <v>802</v>
       </c>
@@ -37650,7 +37752,7 @@
         <v>76.099999999999994</v>
       </c>
     </row>
-    <row r="478" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A478" t="s">
         <v>806</v>
       </c>
@@ -37724,7 +37826,7 @@
         <v>88.4</v>
       </c>
     </row>
-    <row r="479" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A479" t="s">
         <v>248</v>
       </c>
@@ -37777,7 +37879,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="480" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A480" t="s">
         <v>248</v>
       </c>
@@ -37830,7 +37932,7 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="481" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A481" t="s">
         <v>248</v>
       </c>
@@ -37883,15 +37985,15 @@
         <v>94.3</v>
       </c>
     </row>
-    <row r="482" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A482" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B482" t="s">
         <v>911</v>
       </c>
       <c r="C482" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="D482" t="s">
         <v>89</v>
@@ -37936,7 +38038,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="483" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A483" t="s">
         <v>810</v>
       </c>
@@ -38001,7 +38103,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="484" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A484" t="s">
         <v>250</v>
       </c>
@@ -38063,7 +38165,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="485" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A485" t="s">
         <v>252</v>
       </c>
@@ -38116,7 +38218,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="486" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A486" t="s">
         <v>814</v>
       </c>
@@ -38184,7 +38286,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="487" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A487" t="s">
         <v>254</v>
       </c>
@@ -38252,7 +38354,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="488" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A488" t="s">
         <v>925</v>
       </c>
@@ -38311,7 +38413,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="489" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A489" t="s">
         <v>925</v>
       </c>
@@ -38370,7 +38472,7 @@
         <v>74091</v>
       </c>
     </row>
-    <row r="490" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A490" t="s">
         <v>821</v>
       </c>
@@ -38420,7 +38522,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="491" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A491" t="s">
         <v>821</v>
       </c>
@@ -38473,7 +38575,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="492" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A492" t="s">
         <v>821</v>
       </c>
@@ -38526,7 +38628,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="493" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A493" t="s">
         <v>255</v>
       </c>
@@ -38579,7 +38681,7 @@
         <v>2159.6999999999998</v>
       </c>
     </row>
-    <row r="494" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A494" t="s">
         <v>1010</v>
       </c>
@@ -38587,7 +38689,7 @@
         <v>1011</v>
       </c>
       <c r="C494" t="s">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="D494" t="s">
         <v>89</v>
@@ -38608,10 +38710,10 @@
         <v>89</v>
       </c>
       <c r="O494" t="s">
-        <v>379</v>
+        <v>1058</v>
       </c>
       <c r="P494" t="s">
-        <v>218</v>
+        <v>1041</v>
       </c>
       <c r="R494" t="s">
         <v>89</v>
@@ -38619,74 +38721,50 @@
       <c r="T494" t="s">
         <v>89</v>
       </c>
-      <c r="Y494">
-        <v>5.7</v>
-      </c>
-      <c r="Z494">
-        <v>10.4</v>
-      </c>
-      <c r="AA494">
-        <v>-0.3</v>
-      </c>
-      <c r="AB494">
-        <v>3.7</v>
-      </c>
-      <c r="AC494">
-        <v>6.9</v>
-      </c>
-      <c r="AD494">
-        <v>6.8</v>
-      </c>
-      <c r="AE494">
-        <v>5.3</v>
-      </c>
-      <c r="AF494">
-        <v>7.6</v>
-      </c>
       <c r="AG494">
-        <v>4.0999999999999996</v>
+        <v>-6.9</v>
       </c>
       <c r="AH494">
-        <v>4.0999999999999996</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="AI494">
-        <v>5.8</v>
+        <v>-7.5</v>
       </c>
       <c r="AJ494">
-        <v>5.5</v>
+        <v>-11.3</v>
       </c>
       <c r="AK494">
-        <v>2.8</v>
+        <v>-12.6</v>
       </c>
       <c r="AL494">
-        <v>3.3</v>
+        <v>-15.2</v>
       </c>
       <c r="AM494">
-        <v>1.3</v>
+        <v>-9.5</v>
       </c>
       <c r="AN494">
-        <v>5.8</v>
+        <v>-10.1</v>
       </c>
       <c r="AO494">
-        <v>6.8</v>
+        <v>-11.9</v>
       </c>
       <c r="AP494">
-        <v>-5.7</v>
+        <v>-12.1</v>
       </c>
       <c r="AQ494">
-        <v>8.3000000000000007</v>
+        <v>-11.2</v>
       </c>
       <c r="AR494">
-        <v>5.7</v>
+        <v>-9.4</v>
       </c>
       <c r="AS494">
-        <v>5.9</v>
+        <v>-11.7</v>
       </c>
       <c r="AT494">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="495" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>-11.6</v>
+      </c>
+    </row>
+    <row r="495" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A495" t="s">
         <v>1010</v>
       </c>
@@ -38694,13 +38772,13 @@
         <v>1011</v>
       </c>
       <c r="C495" t="s">
-        <v>1013</v>
+        <v>1037</v>
       </c>
       <c r="D495" t="s">
         <v>89</v>
       </c>
       <c r="E495" t="s">
-        <v>258</v>
+        <v>356</v>
       </c>
       <c r="G495" t="s">
         <v>89</v>
@@ -38715,10 +38793,10 @@
         <v>89</v>
       </c>
       <c r="O495" t="s">
-        <v>380</v>
+        <v>1058</v>
       </c>
       <c r="P495" t="s">
-        <v>383</v>
+        <v>1038</v>
       </c>
       <c r="R495" t="s">
         <v>89</v>
@@ -38726,32 +38804,41 @@
       <c r="T495" t="s">
         <v>89</v>
       </c>
+      <c r="AJ495" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AK495">
+        <v>-7.9</v>
+      </c>
+      <c r="AL495">
+        <v>-4.9000000000000004</v>
+      </c>
       <c r="AM495">
-        <v>17.3</v>
+        <v>74.099999999999994</v>
       </c>
       <c r="AN495">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="AO495">
-        <v>15.2</v>
+        <v>30.4</v>
       </c>
       <c r="AP495">
-        <v>17.899999999999999</v>
+        <v>-36.700000000000003</v>
       </c>
       <c r="AQ495">
-        <v>20.9</v>
+        <v>-277.2</v>
       </c>
       <c r="AR495">
-        <v>20.5</v>
+        <v>56.9</v>
       </c>
       <c r="AS495" s="7">
-        <v>17.238670957604757</v>
-      </c>
-      <c r="AT495" s="7">
-        <v>14.93</v>
-      </c>
-    </row>
-    <row r="496" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="AT495">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="496" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A496" t="s">
         <v>1010</v>
       </c>
@@ -38759,13 +38846,13 @@
         <v>1011</v>
       </c>
       <c r="C496" t="s">
-        <v>1014</v>
+        <v>1039</v>
       </c>
       <c r="D496" t="s">
         <v>89</v>
       </c>
       <c r="E496" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="G496" t="s">
         <v>89</v>
@@ -38780,10 +38867,10 @@
         <v>89</v>
       </c>
       <c r="O496" t="s">
-        <v>1015</v>
+        <v>1058</v>
       </c>
       <c r="P496" t="s">
-        <v>1016</v>
+        <v>1040</v>
       </c>
       <c r="R496" t="s">
         <v>89</v>
@@ -38791,55 +38878,58 @@
       <c r="T496" t="s">
         <v>89</v>
       </c>
-      <c r="AH496" s="7">
-        <v>88.287508626875805</v>
+      <c r="AG496">
+        <v>1.6</v>
+      </c>
+      <c r="AH496">
+        <v>3.5</v>
       </c>
       <c r="AI496" s="7">
-        <v>95.363194149188089</v>
-      </c>
-      <c r="AJ496" s="7">
-        <v>100</v>
-      </c>
-      <c r="AK496" s="7">
-        <v>100.2182640302138</v>
-      </c>
-      <c r="AL496" s="7">
-        <v>106.36953362639186</v>
+        <v>3</v>
+      </c>
+      <c r="AJ496">
+        <v>3.8</v>
+      </c>
+      <c r="AK496">
+        <v>1.9</v>
+      </c>
+      <c r="AL496">
+        <v>3.2</v>
       </c>
       <c r="AM496" s="7">
-        <v>120.59536990275485</v>
-      </c>
-      <c r="AN496" s="7">
-        <v>119.06856746525105</v>
-      </c>
-      <c r="AO496" s="7">
-        <v>118.54806010631745</v>
-      </c>
-      <c r="AP496" s="7">
-        <v>134.51579484409552</v>
-      </c>
-      <c r="AQ496" s="7">
-        <v>137.5345635175938</v>
-      </c>
-      <c r="AR496" s="7">
-        <v>143.30285798911947</v>
+        <v>3</v>
+      </c>
+      <c r="AN496">
+        <v>3.8</v>
+      </c>
+      <c r="AO496">
+        <v>2.5</v>
+      </c>
+      <c r="AP496">
+        <v>1.5</v>
+      </c>
+      <c r="AQ496">
+        <v>2.1</v>
+      </c>
+      <c r="AR496">
+        <v>2.2999999999999998</v>
       </c>
       <c r="AS496" s="7">
-        <v>186.71301169804616</v>
+        <v>3.2</v>
       </c>
       <c r="AT496" s="7">
-        <v>192.64827843087079</v>
-      </c>
-    </row>
-    <row r="497" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="497" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A497" t="s">
-        <v>963</v>
+        <v>1010</v>
       </c>
       <c r="B497" t="s">
-        <v>964</v>
+        <v>1011</v>
       </c>
       <c r="C497" t="s">
-        <v>965</v>
+        <v>1042</v>
       </c>
       <c r="D497" t="s">
         <v>89</v>
@@ -38860,101 +38950,1640 @@
         <v>89</v>
       </c>
       <c r="O497" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P497" t="s">
+        <v>1043</v>
+      </c>
+      <c r="R497" t="s">
+        <v>89</v>
+      </c>
+      <c r="T497" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG497">
+        <v>18.8</v>
+      </c>
+      <c r="AH497">
+        <v>19.5</v>
+      </c>
+      <c r="AI497" s="7">
+        <v>26.8</v>
+      </c>
+      <c r="AJ497">
+        <v>28.7</v>
+      </c>
+      <c r="AK497">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="AL497">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AM497" s="7">
+        <v>41.8</v>
+      </c>
+      <c r="AN497">
+        <v>45.7</v>
+      </c>
+      <c r="AO497">
+        <v>50.8</v>
+      </c>
+      <c r="AP497">
+        <v>67.2</v>
+      </c>
+      <c r="AQ497" s="7">
+        <v>69</v>
+      </c>
+      <c r="AR497">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="AS497" s="7">
+        <v>70</v>
+      </c>
+      <c r="AT497" s="7">
+        <v>75.8</v>
+      </c>
+    </row>
+    <row r="498" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A498" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D498" t="s">
+        <v>89</v>
+      </c>
+      <c r="E498" t="s">
+        <v>258</v>
+      </c>
+      <c r="G498" t="s">
+        <v>89</v>
+      </c>
+      <c r="H498" t="s">
+        <v>104</v>
+      </c>
+      <c r="L498" t="s">
+        <v>89</v>
+      </c>
+      <c r="N498" t="s">
+        <v>89</v>
+      </c>
+      <c r="O498" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P498" t="s">
+        <v>1045</v>
+      </c>
+      <c r="R498" t="s">
+        <v>89</v>
+      </c>
+      <c r="T498" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG498">
+        <v>17.3</v>
+      </c>
+      <c r="AH498">
+        <v>18.5</v>
+      </c>
+      <c r="AI498" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="AJ498">
+        <v>25.6</v>
+      </c>
+      <c r="AK498">
+        <v>28.3</v>
+      </c>
+      <c r="AL498">
+        <v>48.1</v>
+      </c>
+      <c r="AM498" s="7">
+        <v>50.9</v>
+      </c>
+      <c r="AN498">
+        <v>55.4</v>
+      </c>
+      <c r="AO498">
+        <v>59.7</v>
+      </c>
+      <c r="AP498" s="7">
+        <v>75</v>
+      </c>
+      <c r="AQ498" s="7">
+        <v>76.3</v>
+      </c>
+      <c r="AR498" s="7">
+        <v>68</v>
+      </c>
+      <c r="AS498" s="7">
+        <v>79.2</v>
+      </c>
+      <c r="AT498" s="7">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="499" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A499" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C499" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D499" t="s">
+        <v>89</v>
+      </c>
+      <c r="E499" t="s">
+        <v>258</v>
+      </c>
+      <c r="G499" t="s">
+        <v>89</v>
+      </c>
+      <c r="H499" t="s">
+        <v>104</v>
+      </c>
+      <c r="L499" t="s">
+        <v>89</v>
+      </c>
+      <c r="N499" t="s">
+        <v>89</v>
+      </c>
+      <c r="O499" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P499" t="s">
+        <v>1047</v>
+      </c>
+      <c r="R499" t="s">
+        <v>89</v>
+      </c>
+      <c r="T499" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI499" s="7"/>
+      <c r="AM499" s="7">
+        <v>21.4</v>
+      </c>
+      <c r="AN499">
+        <v>25.5</v>
+      </c>
+      <c r="AO499">
+        <v>24.1</v>
+      </c>
+      <c r="AP499" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="AQ499" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="AR499" s="7">
+        <v>21.7</v>
+      </c>
+      <c r="AS499" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="AT499" s="7">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A500" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C500" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D500" t="s">
+        <v>89</v>
+      </c>
+      <c r="E500" t="s">
+        <v>279</v>
+      </c>
+      <c r="G500" t="s">
+        <v>89</v>
+      </c>
+      <c r="H500" t="s">
+        <v>104</v>
+      </c>
+      <c r="L500" t="s">
+        <v>89</v>
+      </c>
+      <c r="N500" t="s">
+        <v>89</v>
+      </c>
+      <c r="O500" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P500" t="s">
+        <v>1049</v>
+      </c>
+      <c r="R500" t="s">
+        <v>89</v>
+      </c>
+      <c r="T500" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG500">
+        <v>5.3</v>
+      </c>
+      <c r="AH500">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AI500" s="7">
+        <v>4.8</v>
+      </c>
+      <c r="AJ500">
+        <v>3.9</v>
+      </c>
+      <c r="AK500">
+        <v>3.6</v>
+      </c>
+      <c r="AL500">
+        <v>3.9</v>
+      </c>
+      <c r="AM500" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="AN500">
+        <v>4.5</v>
+      </c>
+      <c r="AO500">
+        <v>5.9</v>
+      </c>
+      <c r="AP500" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="AQ500" s="7">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AR500" s="7">
+        <v>4.3</v>
+      </c>
+      <c r="AS500" s="7">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="AT500" s="7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="501" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A501" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C501" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D501" t="s">
+        <v>89</v>
+      </c>
+      <c r="E501" t="s">
+        <v>258</v>
+      </c>
+      <c r="G501" t="s">
+        <v>89</v>
+      </c>
+      <c r="H501" t="s">
+        <v>104</v>
+      </c>
+      <c r="L501" t="s">
+        <v>89</v>
+      </c>
+      <c r="N501" t="s">
+        <v>89</v>
+      </c>
+      <c r="O501" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P501" t="s">
+        <v>1051</v>
+      </c>
+      <c r="R501" t="s">
+        <v>89</v>
+      </c>
+      <c r="T501" t="s">
+        <v>89</v>
+      </c>
+      <c r="AH501" s="7">
+        <v>14</v>
+      </c>
+      <c r="AI501" s="7">
+        <v>15.5</v>
+      </c>
+      <c r="AJ501">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="AK501">
+        <v>21.1</v>
+      </c>
+      <c r="AL501">
+        <v>7.6</v>
+      </c>
+      <c r="AM501" s="7">
+        <v>12.4</v>
+      </c>
+      <c r="AN501">
+        <v>15.6</v>
+      </c>
+      <c r="AO501">
+        <v>15.4</v>
+      </c>
+      <c r="AP501" s="7">
+        <v>18</v>
+      </c>
+      <c r="AQ501" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="AR501" s="7">
+        <v>22.5</v>
+      </c>
+      <c r="AS501" s="7">
+        <v>22.8</v>
+      </c>
+      <c r="AT501" s="7">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="502" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A502" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C502" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D502" t="s">
+        <v>89</v>
+      </c>
+      <c r="E502" t="s">
+        <v>258</v>
+      </c>
+      <c r="G502" t="s">
+        <v>89</v>
+      </c>
+      <c r="H502" t="s">
+        <v>104</v>
+      </c>
+      <c r="L502" t="s">
+        <v>89</v>
+      </c>
+      <c r="N502" t="s">
+        <v>89</v>
+      </c>
+      <c r="O502" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P502" t="s">
+        <v>1053</v>
+      </c>
+      <c r="R502" t="s">
+        <v>89</v>
+      </c>
+      <c r="T502" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG502">
+        <v>5.7</v>
+      </c>
+      <c r="AH502" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="AI502" s="7">
+        <v>4.2</v>
+      </c>
+      <c r="AJ502" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="AK502" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="AL502" s="7">
+        <v>5.7</v>
+      </c>
+      <c r="AM502" s="7">
+        <v>4.8</v>
+      </c>
+      <c r="AN502" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="AO502" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="AP502" s="7">
+        <v>7.7</v>
+      </c>
+      <c r="AQ502" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="AR502" s="7">
+        <v>13.9</v>
+      </c>
+      <c r="AS502" s="7">
+        <v>14</v>
+      </c>
+      <c r="AT502" s="7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="503" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A503" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D503" t="s">
+        <v>89</v>
+      </c>
+      <c r="E503" t="s">
+        <v>258</v>
+      </c>
+      <c r="G503" t="s">
+        <v>89</v>
+      </c>
+      <c r="H503" t="s">
+        <v>104</v>
+      </c>
+      <c r="L503" t="s">
+        <v>89</v>
+      </c>
+      <c r="N503" t="s">
+        <v>89</v>
+      </c>
+      <c r="O503" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P503" t="s">
+        <v>1055</v>
+      </c>
+      <c r="R503" t="s">
+        <v>89</v>
+      </c>
+      <c r="T503" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG503" s="7">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="AH503" s="7">
+        <v>-7.9</v>
+      </c>
+      <c r="AI503" s="7">
+        <v>-8.8000000000000007</v>
+      </c>
+      <c r="AJ503" s="7">
+        <v>-3.9</v>
+      </c>
+      <c r="AK503" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="AL503" s="7">
+        <v>-3.4</v>
+      </c>
+      <c r="AM503" s="7">
+        <v>-4.3</v>
+      </c>
+      <c r="AN503" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="AO503" s="7">
+        <v>-5.9</v>
+      </c>
+      <c r="AP503" s="7">
+        <v>-7.8</v>
+      </c>
+      <c r="AQ503" s="7">
+        <v>-7.5</v>
+      </c>
+      <c r="AR503" s="7">
+        <v>-8</v>
+      </c>
+      <c r="AS503" s="7">
+        <v>-6.4</v>
+      </c>
+      <c r="AT503" s="7">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="504" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A504" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D504" t="s">
+        <v>89</v>
+      </c>
+      <c r="E504" t="s">
+        <v>258</v>
+      </c>
+      <c r="G504" t="s">
+        <v>89</v>
+      </c>
+      <c r="H504" t="s">
+        <v>104</v>
+      </c>
+      <c r="L504" t="s">
+        <v>89</v>
+      </c>
+      <c r="N504" t="s">
+        <v>89</v>
+      </c>
+      <c r="O504" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P504" t="s">
+        <v>1057</v>
+      </c>
+      <c r="R504" t="s">
+        <v>89</v>
+      </c>
+      <c r="T504" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG504">
+        <v>4.7</v>
+      </c>
+      <c r="AH504" s="7">
+        <v>5.2</v>
+      </c>
+      <c r="AI504" s="7">
+        <v>5.7</v>
+      </c>
+      <c r="AJ504">
+        <v>13.6</v>
+      </c>
+      <c r="AK504">
+        <v>14.2</v>
+      </c>
+      <c r="AL504">
+        <v>15.3</v>
+      </c>
+      <c r="AM504" s="7">
+        <v>14.5</v>
+      </c>
+      <c r="AN504" s="7">
+        <v>15</v>
+      </c>
+      <c r="AO504">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AP504" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="AQ504" s="7">
+        <v>15.8</v>
+      </c>
+      <c r="AR504" s="7">
+        <v>15.7</v>
+      </c>
+      <c r="AS504" s="7">
+        <v>15</v>
+      </c>
+      <c r="AT504" s="7">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="505" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A505" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D505" t="s">
+        <v>89</v>
+      </c>
+      <c r="E505" t="s">
+        <v>258</v>
+      </c>
+      <c r="G505" t="s">
+        <v>89</v>
+      </c>
+      <c r="H505" t="s">
+        <v>104</v>
+      </c>
+      <c r="L505" t="s">
+        <v>89</v>
+      </c>
+      <c r="N505" t="s">
+        <v>89</v>
+      </c>
+      <c r="O505" t="s">
+        <v>379</v>
+      </c>
+      <c r="P505" t="s">
+        <v>1064</v>
+      </c>
+      <c r="R505" t="s">
+        <v>89</v>
+      </c>
+      <c r="T505" t="s">
+        <v>89</v>
+      </c>
+      <c r="V505">
+        <v>4</v>
+      </c>
+      <c r="W505">
+        <v>9</v>
+      </c>
+      <c r="X505">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="Y505">
+        <v>12</v>
+      </c>
+      <c r="Z505">
+        <v>10</v>
+      </c>
+      <c r="AA505">
+        <v>10</v>
+      </c>
+      <c r="AB505">
+        <v>9</v>
+      </c>
+      <c r="AC505">
+        <v>1</v>
+      </c>
+      <c r="AD505">
+        <v>2</v>
+      </c>
+      <c r="AE505">
+        <v>12</v>
+      </c>
+      <c r="AF505">
+        <v>10</v>
+      </c>
+      <c r="AG505">
+        <v>4</v>
+      </c>
+      <c r="AH505" s="8">
+        <v>16</v>
+      </c>
+      <c r="AI505" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ505">
+        <v>21</v>
+      </c>
+      <c r="AK505">
+        <v>5</v>
+      </c>
+      <c r="AL505">
+        <v>9</v>
+      </c>
+      <c r="AM505" s="8">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AN505" s="8">
+        <v>5</v>
+      </c>
+      <c r="AO505">
+        <v>18</v>
+      </c>
+      <c r="AP505" s="8">
+        <v>2</v>
+      </c>
+      <c r="AQ505" s="8">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="AR505" s="8">
+        <v>10</v>
+      </c>
+      <c r="AS505" s="8">
+        <v>1</v>
+      </c>
+      <c r="AT505" s="8">
+        <v>14.000000000000002</v>
+      </c>
+    </row>
+    <row r="506" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A506" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C506" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D506" t="s">
+        <v>89</v>
+      </c>
+      <c r="E506" t="s">
+        <v>258</v>
+      </c>
+      <c r="G506" t="s">
+        <v>89</v>
+      </c>
+      <c r="H506" t="s">
+        <v>104</v>
+      </c>
+      <c r="L506" t="s">
+        <v>89</v>
+      </c>
+      <c r="N506" t="s">
+        <v>89</v>
+      </c>
+      <c r="O506" t="s">
+        <v>379</v>
+      </c>
+      <c r="P506" t="s">
+        <v>1065</v>
+      </c>
+      <c r="R506" t="s">
+        <v>89</v>
+      </c>
+      <c r="T506" t="s">
+        <v>89</v>
+      </c>
+      <c r="V506">
+        <v>15</v>
+      </c>
+      <c r="W506">
+        <v>0</v>
+      </c>
+      <c r="X506">
+        <v>13</v>
+      </c>
+      <c r="Y506">
+        <v>-8</v>
+      </c>
+      <c r="Z506">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AA506">
+        <v>9</v>
+      </c>
+      <c r="AB506" s="8">
+        <v>14.000000000000002</v>
+      </c>
+      <c r="AC506">
+        <v>0</v>
+      </c>
+      <c r="AD506">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AE506">
+        <v>13</v>
+      </c>
+      <c r="AF506">
+        <v>4</v>
+      </c>
+      <c r="AG506">
+        <v>9</v>
+      </c>
+      <c r="AH506" s="8">
+        <v>9</v>
+      </c>
+      <c r="AI506" s="8">
+        <v>9</v>
+      </c>
+      <c r="AJ506">
+        <v>8</v>
+      </c>
+      <c r="AK506" s="8">
+        <v>16</v>
+      </c>
+      <c r="AL506">
+        <v>4</v>
+      </c>
+      <c r="AM506" s="8">
+        <v>-5</v>
+      </c>
+      <c r="AN506" s="8">
+        <v>8</v>
+      </c>
+      <c r="AO506">
+        <v>2</v>
+      </c>
+      <c r="AP506" s="8">
+        <v>4</v>
+      </c>
+      <c r="AQ506" s="8">
+        <v>-6</v>
+      </c>
+      <c r="AR506" s="8">
+        <v>-2</v>
+      </c>
+      <c r="AS506" s="8">
+        <v>11</v>
+      </c>
+      <c r="AT506" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="507" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A507" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C507" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D507" t="s">
+        <v>89</v>
+      </c>
+      <c r="E507" t="s">
+        <v>258</v>
+      </c>
+      <c r="G507" t="s">
+        <v>89</v>
+      </c>
+      <c r="H507" t="s">
+        <v>104</v>
+      </c>
+      <c r="L507" t="s">
+        <v>89</v>
+      </c>
+      <c r="N507" t="s">
+        <v>89</v>
+      </c>
+      <c r="O507" t="s">
+        <v>379</v>
+      </c>
+      <c r="P507" t="s">
+        <v>1066</v>
+      </c>
+      <c r="R507" t="s">
+        <v>89</v>
+      </c>
+      <c r="T507" t="s">
+        <v>89</v>
+      </c>
+      <c r="V507">
+        <v>17</v>
+      </c>
+      <c r="W507">
+        <v>0</v>
+      </c>
+      <c r="X507">
+        <v>8</v>
+      </c>
+      <c r="Y507">
+        <v>10</v>
+      </c>
+      <c r="Z507">
+        <v>12</v>
+      </c>
+      <c r="AA507">
+        <v>16</v>
+      </c>
+      <c r="AB507" s="8">
+        <v>24</v>
+      </c>
+      <c r="AC507">
+        <v>28.000000000000004</v>
+      </c>
+      <c r="AD507">
+        <v>33</v>
+      </c>
+      <c r="AE507">
+        <v>3</v>
+      </c>
+      <c r="AF507">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AG507">
+        <v>9</v>
+      </c>
+      <c r="AH507" s="8">
+        <v>22</v>
+      </c>
+      <c r="AI507" s="8">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AJ507">
+        <v>5</v>
+      </c>
+      <c r="AK507" s="8">
+        <v>19</v>
+      </c>
+      <c r="AL507">
+        <v>9</v>
+      </c>
+      <c r="AM507" s="8">
+        <v>-10</v>
+      </c>
+      <c r="AN507" s="8">
+        <v>6</v>
+      </c>
+      <c r="AO507">
+        <v>32</v>
+      </c>
+      <c r="AP507" s="8">
+        <v>-5</v>
+      </c>
+      <c r="AQ507" s="8">
+        <v>16</v>
+      </c>
+      <c r="AR507" s="8">
+        <v>23</v>
+      </c>
+      <c r="AS507" s="8">
+        <v>15</v>
+      </c>
+      <c r="AT507" s="8">
+        <v>7.0000000000000009</v>
+      </c>
+    </row>
+    <row r="508" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A508" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C508" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D508" t="s">
+        <v>89</v>
+      </c>
+      <c r="E508" t="s">
+        <v>258</v>
+      </c>
+      <c r="G508" t="s">
+        <v>89</v>
+      </c>
+      <c r="H508" t="s">
+        <v>104</v>
+      </c>
+      <c r="L508" t="s">
+        <v>89</v>
+      </c>
+      <c r="N508" t="s">
+        <v>89</v>
+      </c>
+      <c r="O508" t="s">
+        <v>379</v>
+      </c>
+      <c r="P508" t="s">
+        <v>1067</v>
+      </c>
+      <c r="R508" t="s">
+        <v>89</v>
+      </c>
+      <c r="T508" t="s">
+        <v>89</v>
+      </c>
+      <c r="V508">
+        <v>0</v>
+      </c>
+      <c r="W508">
+        <v>40</v>
+      </c>
+      <c r="X508">
+        <v>5</v>
+      </c>
+      <c r="Y508">
+        <v>20</v>
+      </c>
+      <c r="Z508">
+        <v>32</v>
+      </c>
+      <c r="AA508">
+        <v>11</v>
+      </c>
+      <c r="AB508" s="8">
+        <v>2</v>
+      </c>
+      <c r="AC508">
+        <v>44</v>
+      </c>
+      <c r="AD508">
+        <v>-12</v>
+      </c>
+      <c r="AE508">
+        <v>-3</v>
+      </c>
+      <c r="AF508">
+        <v>8</v>
+      </c>
+      <c r="AG508">
+        <v>24</v>
+      </c>
+      <c r="AH508" s="8">
+        <v>9</v>
+      </c>
+      <c r="AI508" s="8">
+        <v>19</v>
+      </c>
+      <c r="AJ508">
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="AK508" s="8">
+        <v>6</v>
+      </c>
+      <c r="AL508">
+        <v>13</v>
+      </c>
+      <c r="AM508" s="8">
+        <v>42</v>
+      </c>
+      <c r="AN508" s="8">
+        <v>11</v>
+      </c>
+      <c r="AO508">
+        <v>20</v>
+      </c>
+      <c r="AP508" s="8">
+        <v>-10</v>
+      </c>
+      <c r="AQ508" s="8">
+        <v>2</v>
+      </c>
+      <c r="AR508" s="8">
+        <v>57.999999999999993</v>
+      </c>
+      <c r="AS508" s="8">
+        <v>20</v>
+      </c>
+      <c r="AT508" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="509" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A509" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C509" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D509" t="s">
+        <v>89</v>
+      </c>
+      <c r="E509" t="s">
+        <v>258</v>
+      </c>
+      <c r="G509" t="s">
+        <v>89</v>
+      </c>
+      <c r="H509" t="s">
+        <v>104</v>
+      </c>
+      <c r="L509" t="s">
+        <v>89</v>
+      </c>
+      <c r="N509" t="s">
+        <v>89</v>
+      </c>
+      <c r="O509" t="s">
+        <v>379</v>
+      </c>
+      <c r="P509" t="s">
+        <v>1068</v>
+      </c>
+      <c r="R509" t="s">
+        <v>89</v>
+      </c>
+      <c r="T509" t="s">
+        <v>89</v>
+      </c>
+      <c r="V509">
+        <v>24</v>
+      </c>
+      <c r="W509">
+        <v>-5</v>
+      </c>
+      <c r="X509">
+        <v>9</v>
+      </c>
+      <c r="Y509">
+        <v>-13</v>
+      </c>
+      <c r="Z509">
+        <v>21</v>
+      </c>
+      <c r="AA509">
+        <v>12</v>
+      </c>
+      <c r="AB509" s="8">
+        <v>23</v>
+      </c>
+      <c r="AC509">
+        <v>13</v>
+      </c>
+      <c r="AD509">
+        <v>-3</v>
+      </c>
+      <c r="AE509">
+        <v>17</v>
+      </c>
+      <c r="AF509">
+        <v>2</v>
+      </c>
+      <c r="AG509">
+        <v>18</v>
+      </c>
+      <c r="AH509" s="8">
+        <v>19</v>
+      </c>
+      <c r="AI509" s="8">
+        <v>9</v>
+      </c>
+      <c r="AJ509">
+        <v>15</v>
+      </c>
+      <c r="AK509" s="8">
+        <v>23</v>
+      </c>
+      <c r="AL509">
+        <v>8</v>
+      </c>
+      <c r="AM509" s="8">
+        <v>6</v>
+      </c>
+      <c r="AN509" s="8">
+        <v>8</v>
+      </c>
+      <c r="AO509">
+        <v>18</v>
+      </c>
+      <c r="AP509" s="8">
+        <v>-4</v>
+      </c>
+      <c r="AQ509" s="8">
+        <v>-12</v>
+      </c>
+      <c r="AR509" s="8">
+        <v>12</v>
+      </c>
+      <c r="AS509" s="8">
+        <v>26</v>
+      </c>
+      <c r="AT509" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="510" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A510" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C510" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D510" t="s">
+        <v>89</v>
+      </c>
+      <c r="E510" t="s">
+        <v>258</v>
+      </c>
+      <c r="G510" t="s">
+        <v>89</v>
+      </c>
+      <c r="H510" t="s">
+        <v>104</v>
+      </c>
+      <c r="L510" t="s">
+        <v>89</v>
+      </c>
+      <c r="N510" t="s">
+        <v>89</v>
+      </c>
+      <c r="O510" t="s">
+        <v>379</v>
+      </c>
+      <c r="P510" t="s">
+        <v>1069</v>
+      </c>
+      <c r="R510" t="s">
+        <v>89</v>
+      </c>
+      <c r="T510" t="s">
+        <v>89</v>
+      </c>
+      <c r="V510">
+        <v>8.4</v>
+      </c>
+      <c r="W510">
+        <v>8.5</v>
+      </c>
+      <c r="X510">
+        <v>13.200000000000001</v>
+      </c>
+      <c r="Y510">
+        <v>2.1999999999999997</v>
+      </c>
+      <c r="Z510">
+        <v>7.3999999999999995</v>
+      </c>
+      <c r="AA510">
+        <v>9.4</v>
+      </c>
+      <c r="AB510">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AC510">
+        <v>7.6</v>
+      </c>
+      <c r="AD510">
+        <v>11.200000000000001</v>
+      </c>
+      <c r="AE510">
+        <v>6.2</v>
+      </c>
+      <c r="AF510">
+        <v>7.3</v>
+      </c>
+      <c r="AG510" s="7">
+        <v>8</v>
+      </c>
+      <c r="AH510">
+        <v>8.6</v>
+      </c>
+      <c r="AI510">
+        <v>4.7</v>
+      </c>
+      <c r="AJ510">
+        <v>5.7</v>
+      </c>
+      <c r="AK510">
+        <v>8.9</v>
+      </c>
+      <c r="AL510">
+        <v>5.7</v>
+      </c>
+      <c r="AM510">
+        <v>4.7</v>
+      </c>
+      <c r="AN510">
+        <v>8.1</v>
+      </c>
+      <c r="AO510">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="AP510">
+        <v>-2.8000000000000003</v>
+      </c>
+      <c r="AQ510">
+        <v>8.4</v>
+      </c>
+      <c r="AR510">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AS510">
+        <v>8.6</v>
+      </c>
+      <c r="AT510">
+        <v>7.1999999999999993</v>
+      </c>
+    </row>
+    <row r="511" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A511" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C511" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D511" t="s">
+        <v>89</v>
+      </c>
+      <c r="E511" t="s">
+        <v>258</v>
+      </c>
+      <c r="G511" t="s">
+        <v>89</v>
+      </c>
+      <c r="H511" t="s">
+        <v>104</v>
+      </c>
+      <c r="L511" t="s">
+        <v>89</v>
+      </c>
+      <c r="N511" t="s">
+        <v>89</v>
+      </c>
+      <c r="O511" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P511" t="s">
+        <v>1072</v>
+      </c>
+      <c r="R511" t="s">
+        <v>89</v>
+      </c>
+      <c r="T511" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG511" s="8">
+        <v>600</v>
+      </c>
+      <c r="AH511" s="8">
+        <v>614</v>
+      </c>
+      <c r="AI511" s="8">
+        <v>647</v>
+      </c>
+      <c r="AJ511" s="8">
+        <v>682</v>
+      </c>
+      <c r="AK511" s="8">
+        <v>720</v>
+      </c>
+      <c r="AL511" s="8">
+        <v>787</v>
+      </c>
+      <c r="AM511" s="8">
+        <v>831</v>
+      </c>
+      <c r="AN511" s="8">
+        <v>861</v>
+      </c>
+      <c r="AO511" s="8">
+        <v>901</v>
+      </c>
+      <c r="AP511" s="8">
+        <v>945</v>
+      </c>
+      <c r="AQ511" s="8">
+        <v>990</v>
+      </c>
+      <c r="AR511" s="8">
+        <v>1033</v>
+      </c>
+      <c r="AS511" s="8">
+        <v>1168</v>
+      </c>
+      <c r="AT511" s="8">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="512" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A512" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C512" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D512" t="s">
+        <v>89</v>
+      </c>
+      <c r="E512" t="s">
+        <v>258</v>
+      </c>
+      <c r="G512" t="s">
+        <v>89</v>
+      </c>
+      <c r="H512" t="s">
+        <v>104</v>
+      </c>
+      <c r="L512" t="s">
+        <v>89</v>
+      </c>
+      <c r="N512" t="s">
+        <v>89</v>
+      </c>
+      <c r="O512" t="s">
+        <v>379</v>
+      </c>
+      <c r="P512" t="s">
+        <v>1074</v>
+      </c>
+      <c r="R512" t="s">
+        <v>89</v>
+      </c>
+      <c r="T512" t="s">
+        <v>89</v>
+      </c>
+      <c r="V512">
+        <v>31</v>
+      </c>
+      <c r="W512">
+        <v>33</v>
+      </c>
+      <c r="X512">
+        <v>31</v>
+      </c>
+      <c r="Y512">
+        <v>32</v>
+      </c>
+      <c r="Z512">
+        <v>37</v>
+      </c>
+      <c r="AA512">
+        <v>38</v>
+      </c>
+      <c r="AB512">
+        <v>34</v>
+      </c>
+      <c r="AC512">
+        <v>37</v>
+      </c>
+      <c r="AD512">
+        <v>38</v>
+      </c>
+      <c r="AE512">
+        <v>37</v>
+      </c>
+      <c r="AF512">
+        <v>38</v>
+      </c>
+      <c r="AG512" s="8">
+        <v>40</v>
+      </c>
+      <c r="AH512" s="8">
+        <v>41</v>
+      </c>
+      <c r="AI512" s="8">
+        <v>44</v>
+      </c>
+      <c r="AJ512" s="8">
+        <v>44</v>
+      </c>
+      <c r="AK512" s="8">
+        <v>45</v>
+      </c>
+      <c r="AL512" s="8">
+        <v>50</v>
+      </c>
+      <c r="AM512" s="8">
+        <v>54</v>
+      </c>
+      <c r="AN512" s="8">
+        <v>48</v>
+      </c>
+      <c r="AO512" s="8">
+        <v>49</v>
+      </c>
+      <c r="AP512" s="8">
+        <v>45</v>
+      </c>
+      <c r="AQ512" s="8">
+        <v>60</v>
+      </c>
+      <c r="AR512" s="8">
+        <v>61</v>
+      </c>
+      <c r="AS512" s="8">
+        <v>67</v>
+      </c>
+      <c r="AT512" s="8">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="513" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A513" t="s">
+        <v>963</v>
+      </c>
+      <c r="B513" t="s">
+        <v>964</v>
+      </c>
+      <c r="C513" t="s">
+        <v>965</v>
+      </c>
+      <c r="D513" t="s">
+        <v>89</v>
+      </c>
+      <c r="E513" t="s">
+        <v>258</v>
+      </c>
+      <c r="G513" t="s">
+        <v>89</v>
+      </c>
+      <c r="H513" t="s">
+        <v>104</v>
+      </c>
+      <c r="L513" t="s">
+        <v>89</v>
+      </c>
+      <c r="N513" t="s">
+        <v>89</v>
+      </c>
+      <c r="O513" t="s">
         <v>981</v>
       </c>
-      <c r="P497" t="s">
+      <c r="P513" t="s">
         <v>966</v>
       </c>
-      <c r="R497" t="s">
-        <v>89</v>
-      </c>
-      <c r="T497" t="s">
-        <v>89</v>
-      </c>
-      <c r="AO497">
+      <c r="R513" t="s">
+        <v>89</v>
+      </c>
+      <c r="T513" t="s">
+        <v>89</v>
+      </c>
+      <c r="AO513">
         <v>24</v>
       </c>
-      <c r="AP497">
+      <c r="AP513">
         <v>27</v>
       </c>
-      <c r="AQ497">
+      <c r="AQ513">
         <v>30</v>
       </c>
-      <c r="AR497">
+      <c r="AR513">
         <v>32</v>
       </c>
-      <c r="AS497">
+      <c r="AS513">
         <v>36</v>
       </c>
     </row>
-    <row r="498" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A498" t="s">
+    <row r="514" spans="1:45" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="A514" t="s">
         <v>843</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B514" t="s">
         <v>844</v>
       </c>
-      <c r="C498" t="s">
+      <c r="C514" t="s">
         <v>917</v>
       </c>
-      <c r="D498" t="s">
-        <v>89</v>
-      </c>
-      <c r="E498" t="s">
+      <c r="D514" t="s">
+        <v>89</v>
+      </c>
+      <c r="E514" t="s">
         <v>356</v>
       </c>
-      <c r="G498" t="s">
-        <v>89</v>
-      </c>
-      <c r="H498" t="s">
-        <v>104</v>
-      </c>
-      <c r="L498" t="s">
-        <v>89</v>
-      </c>
-      <c r="N498" t="s">
-        <v>89</v>
-      </c>
-      <c r="O498" t="s">
+      <c r="G514" t="s">
+        <v>89</v>
+      </c>
+      <c r="H514" t="s">
+        <v>104</v>
+      </c>
+      <c r="L514" t="s">
+        <v>89</v>
+      </c>
+      <c r="N514" t="s">
+        <v>89</v>
+      </c>
+      <c r="O514" t="s">
         <v>845</v>
       </c>
-      <c r="P498" t="s">
+      <c r="P514" t="s">
         <v>918</v>
       </c>
-      <c r="R498" t="s">
-        <v>89</v>
-      </c>
-      <c r="T498" t="s">
-        <v>89</v>
-      </c>
-      <c r="AG498" s="7">
+      <c r="R514" t="s">
+        <v>89</v>
+      </c>
+      <c r="T514" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG514" s="7">
         <v>7956736</v>
       </c>
-      <c r="AH498" s="7">
+      <c r="AH514" s="7">
         <v>10418880</v>
       </c>
-      <c r="AI498" s="7">
+      <c r="AI514" s="7">
         <v>5102809</v>
       </c>
-      <c r="AJ498" s="7">
+      <c r="AJ514" s="7">
         <v>408926</v>
       </c>
-      <c r="AK498" s="7">
+      <c r="AK514" s="7">
         <v>5094083</v>
       </c>
-      <c r="AL498" s="7">
+      <c r="AL514" s="7">
         <v>6574017</v>
       </c>
-      <c r="AM498" s="7">
+      <c r="AM514" s="7">
         <v>8400241.3956557494</v>
       </c>
-      <c r="AN498" s="7">
+      <c r="AN514" s="7">
         <v>7426903.8428782504</v>
       </c>
-      <c r="AO498" s="7">
+      <c r="AO514" s="7">
         <v>5200425.3494196003</v>
       </c>
-      <c r="AP498" s="7">
+      <c r="AP514" s="7">
         <v>520447</v>
       </c>
     </row>
@@ -38971,7 +40600,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="28.1796875" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.81640625" style="1" customWidth="1"/>
@@ -38981,7 +40610,7 @@
     <col min="7" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A1" s="4" t="s">
         <v>116</v>
       </c>
@@ -39002,7 +40631,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A2" s="1" t="s">
         <v>111</v>
       </c>
@@ -39022,7 +40651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A3" s="1" t="s">
         <v>109</v>
       </c>
@@ -39036,7 +40665,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A4" s="1" t="s">
         <v>107</v>
       </c>
@@ -39050,7 +40679,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A5" s="1" t="s">
         <v>105</v>
       </c>
@@ -39064,7 +40693,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A6" s="1" t="s">
         <v>103</v>
       </c>
@@ -39078,7 +40707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A7" s="1" t="s">
         <v>102</v>
       </c>
@@ -39092,7 +40721,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A8" s="1" t="s">
         <v>101</v>
       </c>
@@ -39106,7 +40735,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A9" s="1" t="s">
         <v>99</v>
       </c>
@@ -39120,7 +40749,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A10" s="1" t="s">
         <v>98</v>
       </c>
@@ -39134,7 +40763,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A11" s="1" t="s">
         <v>97</v>
       </c>
@@ -39148,7 +40777,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A12" s="1" t="s">
         <v>96</v>
       </c>
@@ -39162,7 +40791,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A13" s="1" t="s">
         <v>95</v>
       </c>
@@ -39176,7 +40805,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A14" s="1" t="s">
         <v>94</v>
       </c>
@@ -39190,7 +40819,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A15" s="1" t="s">
         <v>93</v>
       </c>
@@ -39204,7 +40833,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.75">
       <c r="A16" s="1" t="s">
         <v>92</v>
       </c>
@@ -39218,7 +40847,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A17" s="1" t="s">
         <v>91</v>
       </c>
@@ -39232,7 +40861,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
@@ -39246,7 +40875,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A19" s="1" t="s">
         <v>86</v>
       </c>
@@ -39260,7 +40889,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A20" s="1" t="s">
         <v>84</v>
       </c>
@@ -39274,7 +40903,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -39288,7 +40917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -39302,7 +40931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A23" s="1" t="s">
         <v>79</v>
       </c>
@@ -39316,7 +40945,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A24" s="1" t="s">
         <v>76</v>
       </c>

--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{644880C9-9EA3-4A32-8448-43B521AA4297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9050FAF0-A523-4F93-9C5B-8D4BAE569DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11356,19 +11356,23 @@
         <v>89</v>
       </c>
       <c r="V2">
-        <v>77.2</v>
+        <v>82.3</v>
       </c>
       <c r="AA2">
-        <v>68.3</v>
-      </c>
-      <c r="AG2">
-        <v>62.3</v>
-      </c>
-      <c r="AJ2">
-        <v>56.8</v>
-      </c>
-      <c r="AM2" s="7">
-        <v>52</v>
+        <v>74.2</v>
+      </c>
+      <c r="AF2">
+        <v>70.2</v>
+      </c>
+      <c r="AI2">
+        <v>65.2</v>
+      </c>
+      <c r="AL2">
+        <v>63.8</v>
+      </c>
+      <c r="AM2" s="7"/>
+      <c r="AS2">
+        <v>38.6</v>
       </c>
     </row>
     <row r="3" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">

--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9050FAF0-A523-4F93-9C5B-8D4BAE569DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A35F557-FEDC-4CCB-A562-0BED45EA2C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3362,10 +3362,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -3489,7 +3490,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3499,6 +3500,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -13806,28 +13809,28 @@
       <c r="T45" t="s">
         <v>89</v>
       </c>
-      <c r="AA45" s="7">
+      <c r="AA45" s="10">
         <v>0.443</v>
       </c>
-      <c r="AF45" s="7">
+      <c r="AF45" s="9">
         <v>0.35</v>
       </c>
-      <c r="AG45" s="7">
+      <c r="AG45" s="9">
         <v>0.24</v>
       </c>
-      <c r="AH45" s="7">
+      <c r="AH45" s="10">
         <v>0.16700000000000001</v>
       </c>
-      <c r="AJ45" s="7">
+      <c r="AJ45" s="9">
         <v>0.17</v>
       </c>
-      <c r="AM45" s="7">
+      <c r="AM45" s="9">
         <v>0.15</v>
       </c>
-      <c r="AR45" s="7">
+      <c r="AR45" s="10">
         <v>0.129</v>
       </c>
-      <c r="AT45" s="7">
+      <c r="AT45" s="10">
         <v>0.13600000000000001</v>
       </c>
     </row>
@@ -13874,22 +13877,22 @@
       <c r="T46" t="s">
         <v>89</v>
       </c>
-      <c r="AG46" s="7">
+      <c r="AG46" s="9">
         <v>0.09</v>
       </c>
-      <c r="AH46" s="7">
+      <c r="AH46" s="10">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AJ46" s="7">
+      <c r="AJ46" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AM46" s="7">
+      <c r="AM46" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AR46" s="7">
+      <c r="AR46" s="10">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="AT46" s="7">
+      <c r="AT46" s="10">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13936,22 +13939,22 @@
       <c r="T47" t="s">
         <v>89</v>
       </c>
-      <c r="AG47" s="7">
+      <c r="AG47" s="9">
         <v>0.27</v>
       </c>
-      <c r="AH47" s="7">
+      <c r="AH47" s="10">
         <v>0.187</v>
       </c>
-      <c r="AJ47" s="7">
+      <c r="AJ47" s="9">
         <v>0.19</v>
       </c>
-      <c r="AM47" s="7">
+      <c r="AM47" s="9">
         <v>0.17</v>
       </c>
-      <c r="AR47" s="7">
+      <c r="AR47" s="10">
         <v>0.159</v>
       </c>
-      <c r="AT47" s="7">
+      <c r="AT47" s="10">
         <v>0.16400000000000001</v>
       </c>
     </row>
@@ -13998,22 +14001,22 @@
       <c r="T48" t="s">
         <v>89</v>
       </c>
-      <c r="AG48" s="7">
+      <c r="AG48" s="9">
         <v>0.12</v>
       </c>
-      <c r="AH48" s="7">
+      <c r="AH48" s="10">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="AJ48" s="7">
+      <c r="AJ48" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AM48" s="7">
+      <c r="AM48" s="9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="AR48" s="7">
+      <c r="AR48" s="10">
         <v>0.04</v>
       </c>
-      <c r="AT48" s="7">
+      <c r="AT48" s="10">
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
@@ -14060,22 +14063,22 @@
       <c r="T49" t="s">
         <v>89</v>
       </c>
-      <c r="AG49" s="7">
+      <c r="AG49" s="9">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AH49" s="7">
+      <c r="AH49" s="10">
         <v>0.17100000000000001</v>
       </c>
-      <c r="AJ49" s="7">
+      <c r="AJ49" s="9">
         <v>0.21</v>
       </c>
-      <c r="AM49" s="7">
+      <c r="AM49" s="9">
         <v>0.19</v>
       </c>
-      <c r="AR49" s="7">
+      <c r="AR49" s="10">
         <v>0.14899999999999999</v>
       </c>
-      <c r="AT49" s="7">
+      <c r="AT49" s="10">
         <v>0.158</v>
       </c>
     </row>
@@ -14122,22 +14125,22 @@
       <c r="T50" t="s">
         <v>89</v>
       </c>
-      <c r="AG50" s="7">
+      <c r="AG50" s="9">
         <v>0.25</v>
       </c>
-      <c r="AH50" s="7">
+      <c r="AH50" s="10">
         <v>0.189</v>
       </c>
-      <c r="AJ50" s="7">
+      <c r="AJ50" s="9">
         <v>0.19</v>
       </c>
-      <c r="AM50" s="7">
+      <c r="AM50" s="9">
         <v>0.16</v>
       </c>
-      <c r="AR50" s="7">
+      <c r="AR50" s="10">
         <v>0.15</v>
       </c>
-      <c r="AT50" s="7">
+      <c r="AT50" s="10">
         <v>0.14899999999999999</v>
       </c>
     </row>
@@ -14184,22 +14187,22 @@
       <c r="T51" t="s">
         <v>89</v>
       </c>
-      <c r="AG51" s="7">
+      <c r="AG51" s="9">
         <v>0.18</v>
       </c>
-      <c r="AH51" s="7">
+      <c r="AH51" s="10">
         <v>0.161</v>
       </c>
-      <c r="AJ51" s="7">
+      <c r="AJ51" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AM51" s="7">
+      <c r="AM51" s="9">
         <v>0.11</v>
       </c>
-      <c r="AR51" s="7">
+      <c r="AR51" s="10">
         <v>0.122</v>
       </c>
-      <c r="AT51" s="7">
+      <c r="AT51" s="10">
         <v>0.123</v>
       </c>
     </row>
@@ -14246,22 +14249,22 @@
       <c r="T52" t="s">
         <v>89</v>
       </c>
-      <c r="AG52" s="7">
+      <c r="AG52" s="9">
         <v>0.26</v>
       </c>
-      <c r="AH52" s="7">
+      <c r="AH52" s="10">
         <v>0.192</v>
       </c>
-      <c r="AJ52" s="7">
+      <c r="AJ52" s="9">
         <v>0.18</v>
       </c>
-      <c r="AM52" s="7">
+      <c r="AM52" s="9">
         <v>0.17</v>
       </c>
-      <c r="AR52" s="7">
+      <c r="AR52" s="10">
         <v>0.15</v>
       </c>
-      <c r="AT52" s="7">
+      <c r="AT52" s="10">
         <v>0.157</v>
       </c>
     </row>

--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200B5422-8A4E-4CAB-8252-D9ECAB22E1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66BD56BF-2C8F-4FB6-A82D-ABD1769F3C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7966" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7966" uniqueCount="1092">
   <si>
     <t>Indicator</t>
   </si>
@@ -3357,6 +3357,51 @@
   </si>
   <si>
     <t>Percentage of farmers with the right to sell or use land as collateral</t>
+  </si>
+  <si>
+    <t>Direct economic loss attributed to disasters in relation to global gross domestic product (GDP)</t>
+  </si>
+  <si>
+    <t>Houses damaged by disaster</t>
+  </si>
+  <si>
+    <t>Ha of crops damaged by disaster</t>
+  </si>
+  <si>
+    <t>Classrooms damaged by disaster</t>
+  </si>
+  <si>
+    <t>Health centers damaged by disaster</t>
+  </si>
+  <si>
+    <t>Bridges damaged by disaster</t>
+  </si>
+  <si>
+    <t>Administrative offices damaged by disaster</t>
+  </si>
+  <si>
+    <t>Transmission lines damaged by disaster</t>
+  </si>
+  <si>
+    <t>Water supply structures damaged by disaster</t>
+  </si>
+  <si>
+    <t>Markets damaged by disaster</t>
+  </si>
+  <si>
+    <t>Factories damaged by disaster</t>
+  </si>
+  <si>
+    <t>Ha of forests damaged by disaster</t>
+  </si>
+  <si>
+    <t>Churches damaged by disaster</t>
+  </si>
+  <si>
+    <t>Road sections damaged by disaster</t>
+  </si>
+  <si>
+    <t>Cattle and livestock lost due to disaster</t>
   </si>
 </sst>
 </file>
@@ -15468,7 +15513,7 @@
         <v>854</v>
       </c>
       <c r="B73" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C73" t="s">
         <v>865</v>
@@ -15495,7 +15540,7 @@
         <v>886</v>
       </c>
       <c r="P73" t="s">
-        <v>912</v>
+        <v>1078</v>
       </c>
       <c r="R73" t="s">
         <v>89</v>
@@ -15530,7 +15575,7 @@
         <v>854</v>
       </c>
       <c r="B74" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C74" t="s">
         <v>869</v>
@@ -15557,7 +15602,7 @@
         <v>886</v>
       </c>
       <c r="P74" t="s">
-        <v>855</v>
+        <v>1079</v>
       </c>
       <c r="R74" t="s">
         <v>89</v>
@@ -15592,7 +15637,7 @@
         <v>854</v>
       </c>
       <c r="B75" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C75" t="s">
         <v>867</v>
@@ -15619,7 +15664,7 @@
         <v>886</v>
       </c>
       <c r="P75" t="s">
-        <v>856</v>
+        <v>1080</v>
       </c>
       <c r="R75" t="s">
         <v>89</v>
@@ -15654,7 +15699,7 @@
         <v>854</v>
       </c>
       <c r="B76" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C76" t="s">
         <v>871</v>
@@ -15681,7 +15726,7 @@
         <v>886</v>
       </c>
       <c r="P76" t="s">
-        <v>857</v>
+        <v>1081</v>
       </c>
       <c r="R76" t="s">
         <v>89</v>
@@ -15716,7 +15761,7 @@
         <v>854</v>
       </c>
       <c r="B77" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C77" t="s">
         <v>868</v>
@@ -15743,7 +15788,7 @@
         <v>886</v>
       </c>
       <c r="P77" t="s">
-        <v>858</v>
+        <v>1082</v>
       </c>
       <c r="R77" t="s">
         <v>89</v>
@@ -15778,7 +15823,7 @@
         <v>854</v>
       </c>
       <c r="B78" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C78" t="s">
         <v>872</v>
@@ -15805,7 +15850,7 @@
         <v>886</v>
       </c>
       <c r="P78" t="s">
-        <v>859</v>
+        <v>1083</v>
       </c>
       <c r="R78" t="s">
         <v>89</v>
@@ -15840,7 +15885,7 @@
         <v>854</v>
       </c>
       <c r="B79" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C79" t="s">
         <v>866</v>
@@ -15867,7 +15912,7 @@
         <v>886</v>
       </c>
       <c r="P79" t="s">
-        <v>860</v>
+        <v>1084</v>
       </c>
       <c r="R79" t="s">
         <v>89</v>
@@ -15902,7 +15947,7 @@
         <v>854</v>
       </c>
       <c r="B80" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C80" t="s">
         <v>870</v>
@@ -15929,7 +15974,7 @@
         <v>886</v>
       </c>
       <c r="P80" t="s">
-        <v>861</v>
+        <v>1085</v>
       </c>
       <c r="R80" t="s">
         <v>89</v>
@@ -15964,7 +16009,7 @@
         <v>854</v>
       </c>
       <c r="B81" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C81" t="s">
         <v>873</v>
@@ -15991,7 +16036,7 @@
         <v>886</v>
       </c>
       <c r="P81" t="s">
-        <v>862</v>
+        <v>1086</v>
       </c>
       <c r="R81" t="s">
         <v>89</v>
@@ -16023,7 +16068,7 @@
         <v>854</v>
       </c>
       <c r="B82" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C82" t="s">
         <v>874</v>
@@ -16050,7 +16095,7 @@
         <v>886</v>
       </c>
       <c r="P82" t="s">
-        <v>863</v>
+        <v>1087</v>
       </c>
       <c r="R82" t="s">
         <v>89</v>
@@ -16082,7 +16127,7 @@
         <v>854</v>
       </c>
       <c r="B83" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C83" t="s">
         <v>875</v>
@@ -16109,7 +16154,7 @@
         <v>886</v>
       </c>
       <c r="P83" t="s">
-        <v>864</v>
+        <v>1088</v>
       </c>
       <c r="R83" t="s">
         <v>89</v>
@@ -16138,7 +16183,7 @@
         <v>854</v>
       </c>
       <c r="B84" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C84" t="s">
         <v>883</v>
@@ -16165,7 +16210,7 @@
         <v>886</v>
       </c>
       <c r="P84" t="s">
-        <v>881</v>
+        <v>1089</v>
       </c>
       <c r="R84" t="s">
         <v>89</v>
@@ -16197,7 +16242,7 @@
         <v>854</v>
       </c>
       <c r="B85" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C85" t="s">
         <v>884</v>
@@ -16224,7 +16269,7 @@
         <v>886</v>
       </c>
       <c r="P85" t="s">
-        <v>913</v>
+        <v>1090</v>
       </c>
       <c r="R85" t="s">
         <v>89</v>
@@ -16256,7 +16301,7 @@
         <v>854</v>
       </c>
       <c r="B86" t="s">
-        <v>853</v>
+        <v>1077</v>
       </c>
       <c r="C86" t="s">
         <v>885</v>
@@ -16283,7 +16328,7 @@
         <v>886</v>
       </c>
       <c r="P86" t="s">
-        <v>882</v>
+        <v>1091</v>
       </c>
       <c r="R86" t="s">
         <v>89</v>
@@ -16350,10 +16395,10 @@
       <c r="T87" t="s">
         <v>89</v>
       </c>
+      <c r="AJ87">
+        <v>73.3</v>
+      </c>
       <c r="AM87">
-        <v>77.3</v>
-      </c>
-      <c r="AN87">
         <v>96.7</v>
       </c>
       <c r="AO87">
@@ -16369,6 +16414,9 @@
         <v>100</v>
       </c>
       <c r="AS87">
+        <v>100</v>
+      </c>
+      <c r="AT87">
         <v>100</v>
       </c>
     </row>

--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B54F145-B73F-431E-8B6B-5AEE4CD57B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C72346-FE13-423F-A1B3-986E79831C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11256,7 +11256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU581"/>
+  <dimension ref="A1:AV581"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="10.6328125" customWidth="1"/>
@@ -11266,7 +11266,7 @@
     <col min="22" max="46" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11405,8 +11405,14 @@
       <c r="AT1" s="2">
         <v>2024</v>
       </c>
-    </row>
-    <row r="2" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="AU1" s="2">
+        <v>2025</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -11466,7 +11472,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -11525,7 +11531,7 @@
         <v>27.4</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -11581,7 +11587,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -11637,7 +11643,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -11693,7 +11699,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -11749,7 +11755,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="8" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -11808,7 +11814,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="9" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11867,7 +11873,7 @@
         <v>31.6</v>
       </c>
     </row>
-    <row r="10" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -11929,7 +11935,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="11" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -11991,7 +11997,7 @@
         <v>34.700000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -12053,7 +12059,7 @@
         <v>37.4</v>
       </c>
     </row>
-    <row r="13" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -12115,7 +12121,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="14" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -12177,7 +12183,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="15" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -12233,7 +12239,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="16" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -16046,7 +16052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A81" t="s">
         <v>849</v>
       </c>
@@ -16105,7 +16111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A82" t="s">
         <v>849</v>
       </c>
@@ -16164,7 +16170,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A83" t="s">
         <v>849</v>
       </c>
@@ -16220,7 +16226,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A84" t="s">
         <v>849</v>
       </c>
@@ -16279,7 +16285,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A85" t="s">
         <v>849</v>
       </c>
@@ -16338,7 +16344,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="86" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A86" t="s">
         <v>849</v>
       </c>
@@ -16397,7 +16403,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="87" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A87" t="s">
         <v>132</v>
       </c>
@@ -16462,7 +16468,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="88" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A88" t="s">
         <v>1085</v>
       </c>
@@ -16539,7 +16545,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="89" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A89" t="s">
         <v>134</v>
       </c>
@@ -16636,8 +16642,14 @@
       <c r="AT89">
         <v>26.6</v>
       </c>
-    </row>
-    <row r="90" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="AU89">
+        <v>24.8</v>
+      </c>
+      <c r="AV89">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A90" t="s">
         <v>134</v>
       </c>
@@ -16731,11 +16743,17 @@
       <c r="AS90">
         <v>7.5</v>
       </c>
-      <c r="AT90">
+      <c r="AT90" s="7">
         <v>7</v>
       </c>
-    </row>
-    <row r="91" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="AU90">
+        <v>7.1</v>
+      </c>
+      <c r="AV90">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A91" t="s">
         <v>134</v>
       </c>
@@ -16832,8 +16850,14 @@
       <c r="AT91">
         <v>4.7</v>
       </c>
-    </row>
-    <row r="92" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="AU91" s="7">
+        <v>4</v>
+      </c>
+      <c r="AV91">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A92" t="s">
         <v>134</v>
       </c>
@@ -16930,8 +16954,14 @@
       <c r="AT92">
         <v>14.9</v>
       </c>
-    </row>
-    <row r="93" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+      <c r="AU92">
+        <v>13.7</v>
+      </c>
+      <c r="AV92">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A93" t="s">
         <v>135</v>
       </c>
@@ -16982,7 +17012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="94" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A94" t="s">
         <v>135</v>
       </c>
@@ -17042,7 +17072,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="95" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A95" t="s">
         <v>135</v>
       </c>
@@ -17096,7 +17126,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="20" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="96" spans="1:48" ht="20" customHeight="1" x14ac:dyDescent="0.75">
       <c r="A96" t="s">
         <v>843</v>
       </c>

--- a/data/2025_RW-SDG_Data.xlsx
+++ b/data/2025_RW-SDG_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GGessienne\Documents\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C72346-FE13-423F-A1B3-986E79831C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C798CD4E-6556-4972-832D-C886FC700565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -45572,7 +45572,7 @@
         <v>110</v>
       </c>
       <c r="G2" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.75">
